--- a/research/traditional_assets/database/data/malaysia/malaysia_auto_truck.xlsx
+++ b/research/traditional_assets/database/data/malaysia/malaysia_auto_truck.xlsx
@@ -1406,7 +1406,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1543,22 +1543,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1060292532576925</v>
+        <v>0.1058089830498741</v>
       </c>
       <c r="C2">
-        <v>2276.219833293896</v>
+        <v>2256.200859956046</v>
       </c>
       <c r="D2">
-        <v>1556.419833293896</v>
+        <v>1562.132859956046</v>
       </c>
       <c r="E2">
-        <v>-2093.3</v>
+        <v>-2067.568</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>25.732</v>
       </c>
       <c r="G2">
         <v>719.8</v>
@@ -1579,28 +1579,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.2943196</v>
       </c>
       <c r="N2">
-        <v>366.4333333333334</v>
+        <v>365.1390137333334</v>
       </c>
       <c r="O2">
-        <v>87.94400000000002</v>
+        <v>87.63336329600001</v>
       </c>
       <c r="P2">
-        <v>278.4893333333334</v>
+        <v>277.5056504373334</v>
       </c>
       <c r="Q2">
-        <v>447.8893333333334</v>
+        <v>446.9056504373334</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1060292532576925</v>
+        <v>0.106491619242297</v>
       </c>
       <c r="T2">
-        <v>1.015551736571413</v>
+        <v>1.02334789131681</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1617,7 +1617,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>283.1088498801481</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1625,22 +1625,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1058089830498741</v>
+        <v>0.1055887128420556</v>
       </c>
       <c r="C3">
-        <v>2256.200859956046</v>
+        <v>2236.223981840198</v>
       </c>
       <c r="D3">
-        <v>1562.132859956046</v>
+        <v>1567.887981840198</v>
       </c>
       <c r="E3">
-        <v>-2067.568</v>
+        <v>-2041.836</v>
       </c>
       <c r="F3">
-        <v>25.732</v>
+        <v>51.46400000000001</v>
       </c>
       <c r="G3">
         <v>719.8</v>
@@ -1661,28 +1661,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M3">
-        <v>1.2943196</v>
+        <v>2.5886392</v>
       </c>
       <c r="N3">
-        <v>365.1390137333334</v>
+        <v>363.8446941333334</v>
       </c>
       <c r="O3">
-        <v>87.63336329600001</v>
+        <v>87.32272659200001</v>
       </c>
       <c r="P3">
-        <v>277.5056504373334</v>
+        <v>276.5219675413334</v>
       </c>
       <c r="Q3">
-        <v>446.9056504373334</v>
+        <v>445.9219675413334</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.106491619242297</v>
+        <v>0.1069634212674037</v>
       </c>
       <c r="T3">
-        <v>1.02334789131681</v>
+        <v>1.031303151261092</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>283.1088498801481</v>
+        <v>141.5544249400741</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1707,22 +1707,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1055887128420556</v>
+        <v>0.1053684426342371</v>
       </c>
       <c r="C4">
-        <v>2236.223981840198</v>
+        <v>2216.28966592129</v>
       </c>
       <c r="D4">
-        <v>1567.887981840198</v>
+        <v>1573.68566592129</v>
       </c>
       <c r="E4">
-        <v>-2041.836</v>
+        <v>-2016.104</v>
       </c>
       <c r="F4">
-        <v>51.46400000000001</v>
+        <v>77.19600000000001</v>
       </c>
       <c r="G4">
         <v>719.8</v>
@@ -1743,28 +1743,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M4">
-        <v>2.5886392</v>
+        <v>3.8829588</v>
       </c>
       <c r="N4">
-        <v>363.8446941333334</v>
+        <v>362.5503745333334</v>
       </c>
       <c r="O4">
-        <v>87.32272659200001</v>
+        <v>87.01208988800002</v>
       </c>
       <c r="P4">
-        <v>276.5219675413334</v>
+        <v>275.5382846453334</v>
       </c>
       <c r="Q4">
-        <v>445.9219675413334</v>
+        <v>444.9382846453334</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1069634212674037</v>
+        <v>0.1074449511693166</v>
       </c>
       <c r="T4">
-        <v>1.031303151261092</v>
+        <v>1.039422437183607</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1781,7 +1781,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>141.5544249400741</v>
+        <v>94.36961662671604</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1789,22 +1789,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1053684426342371</v>
+        <v>0.1051481724264186</v>
       </c>
       <c r="C5">
-        <v>2216.28966592129</v>
+        <v>2196.398386106958</v>
       </c>
       <c r="D5">
-        <v>1573.68566592129</v>
+        <v>1579.526386106958</v>
       </c>
       <c r="E5">
-        <v>-2016.104</v>
+        <v>-1990.372</v>
       </c>
       <c r="F5">
-        <v>77.19600000000001</v>
+        <v>102.928</v>
       </c>
       <c r="G5">
         <v>719.8</v>
@@ -1825,28 +1825,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M5">
-        <v>3.8829588</v>
+        <v>5.177278400000001</v>
       </c>
       <c r="N5">
-        <v>362.5503745333334</v>
+        <v>361.2560549333334</v>
       </c>
       <c r="O5">
-        <v>87.01208988800002</v>
+        <v>86.70145318400002</v>
       </c>
       <c r="P5">
-        <v>275.5382846453334</v>
+        <v>274.5546017493334</v>
       </c>
       <c r="Q5">
-        <v>444.9382846453334</v>
+        <v>443.9546017493334</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1074449511693166</v>
+        <v>0.1079365129441861</v>
       </c>
       <c r="T5">
-        <v>1.039422437183607</v>
+        <v>1.047710874896175</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1863,7 +1863,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>94.36961662671604</v>
+        <v>70.77721247003703</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1871,22 +1871,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1051481724264186</v>
+        <v>0.1049279022186002</v>
       </c>
       <c r="C6">
-        <v>2196.398386106958</v>
+        <v>2176.550623366657</v>
       </c>
       <c r="D6">
-        <v>1579.526386106958</v>
+        <v>1585.410623366656</v>
       </c>
       <c r="E6">
-        <v>-1990.372</v>
+        <v>-1964.64</v>
       </c>
       <c r="F6">
-        <v>102.928</v>
+        <v>128.66</v>
       </c>
       <c r="G6">
         <v>719.8</v>
@@ -1907,28 +1907,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M6">
-        <v>5.177278400000001</v>
+        <v>6.471598000000001</v>
       </c>
       <c r="N6">
-        <v>361.2560549333334</v>
+        <v>359.9617353333334</v>
       </c>
       <c r="O6">
-        <v>86.70145318400002</v>
+        <v>86.39081648</v>
       </c>
       <c r="P6">
-        <v>274.5546017493334</v>
+        <v>273.5709188533334</v>
       </c>
       <c r="Q6">
-        <v>443.9546017493334</v>
+        <v>442.9709188533334</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1079365129441861</v>
+        <v>0.1084384233880002</v>
       </c>
       <c r="T6">
-        <v>1.047710874896175</v>
+        <v>1.05617380603427</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>70.77721247003703</v>
+        <v>56.62176997602962</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1953,22 +1953,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1049279022186002</v>
+        <v>0.1047076320107817</v>
       </c>
       <c r="C7">
-        <v>2176.550623366657</v>
+        <v>2156.746865863701</v>
       </c>
       <c r="D7">
-        <v>1585.410623366656</v>
+        <v>1591.3388658637</v>
       </c>
       <c r="E7">
-        <v>-1964.64</v>
+        <v>-1938.908</v>
       </c>
       <c r="F7">
-        <v>128.66</v>
+        <v>154.392</v>
       </c>
       <c r="G7">
         <v>719.8</v>
@@ -1989,28 +1989,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M7">
-        <v>6.471598000000001</v>
+        <v>7.765917600000001</v>
       </c>
       <c r="N7">
-        <v>359.9617353333334</v>
+        <v>358.6674157333334</v>
       </c>
       <c r="O7">
-        <v>86.39081648</v>
+        <v>86.08017977600001</v>
       </c>
       <c r="P7">
-        <v>273.5709188533334</v>
+        <v>272.5872359573333</v>
       </c>
       <c r="Q7">
-        <v>442.9709188533334</v>
+        <v>441.9872359573334</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1084384233880002</v>
+        <v>0.1089510127774274</v>
       </c>
       <c r="T7">
-        <v>1.05617380603427</v>
+        <v>1.064816799537005</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>56.62176997602962</v>
+        <v>47.18480831335802</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2035,22 +2035,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1047076320107817</v>
+        <v>0.1044873618029633</v>
       </c>
       <c r="C8">
-        <v>2156.746865863701</v>
+        <v>2136.987609090262</v>
       </c>
       <c r="D8">
-        <v>1591.3388658637</v>
+        <v>1597.311609090262</v>
       </c>
       <c r="E8">
-        <v>-1938.908</v>
+        <v>-1913.176</v>
       </c>
       <c r="F8">
-        <v>154.392</v>
+        <v>180.124</v>
       </c>
       <c r="G8">
         <v>719.8</v>
@@ -2071,28 +2071,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M8">
-        <v>7.765917600000001</v>
+        <v>9.0602372</v>
       </c>
       <c r="N8">
-        <v>358.6674157333334</v>
+        <v>357.3730961333334</v>
       </c>
       <c r="O8">
-        <v>86.08017977600001</v>
+        <v>85.769543072</v>
       </c>
       <c r="P8">
-        <v>272.5872359573333</v>
+        <v>271.6035530613334</v>
       </c>
       <c r="Q8">
-        <v>441.9872359573334</v>
+        <v>441.0035530613334</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1089510127774274</v>
+        <v>0.1094746255945842</v>
       </c>
       <c r="T8">
-        <v>1.064816799537005</v>
+        <v>1.073645663867756</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2109,7 +2109,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>47.18480831335802</v>
+        <v>40.44412141144974</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2117,22 +2117,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1044873618029633</v>
+        <v>0.1042670915951448</v>
       </c>
       <c r="C9">
-        <v>2136.987609090262</v>
+        <v>2117.273356005423</v>
       </c>
       <c r="D9">
-        <v>1597.311609090262</v>
+        <v>1603.329356005423</v>
       </c>
       <c r="E9">
-        <v>-1913.176</v>
+        <v>-1887.444</v>
       </c>
       <c r="F9">
-        <v>180.124</v>
+        <v>205.856</v>
       </c>
       <c r="G9">
         <v>719.8</v>
@@ -2153,28 +2153,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M9">
-        <v>9.060237200000001</v>
+        <v>10.3545568</v>
       </c>
       <c r="N9">
-        <v>357.3730961333334</v>
+        <v>356.0787765333334</v>
       </c>
       <c r="O9">
-        <v>85.769543072</v>
+        <v>85.45890636800002</v>
       </c>
       <c r="P9">
-        <v>271.6035530613334</v>
+        <v>270.6198701653334</v>
       </c>
       <c r="Q9">
-        <v>441.0035530613334</v>
+        <v>440.0198701653334</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1094746255945842</v>
+        <v>0.1100096212990704</v>
       </c>
       <c r="T9">
-        <v>1.073645663867756</v>
+        <v>1.082666460031785</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2191,7 +2191,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>40.44412141144973</v>
+        <v>35.38860623501851</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2199,22 +2199,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1042670915951448</v>
+        <v>0.1040468213873263</v>
       </c>
       <c r="C10">
-        <v>2117.273356005423</v>
+        <v>2097.604617176369</v>
       </c>
       <c r="D10">
-        <v>1603.329356005423</v>
+        <v>1609.392617176369</v>
       </c>
       <c r="E10">
-        <v>-1887.444</v>
+        <v>-1861.712</v>
       </c>
       <c r="F10">
-        <v>205.856</v>
+        <v>231.588</v>
       </c>
       <c r="G10">
         <v>719.8</v>
@@ -2235,28 +2235,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M10">
-        <v>10.3545568</v>
+        <v>11.6488764</v>
       </c>
       <c r="N10">
-        <v>356.0787765333334</v>
+        <v>354.7844569333334</v>
       </c>
       <c r="O10">
-        <v>85.45890636800002</v>
+        <v>85.14826966400001</v>
       </c>
       <c r="P10">
-        <v>270.6198701653334</v>
+        <v>269.6361872693334</v>
       </c>
       <c r="Q10">
-        <v>440.0198701653334</v>
+        <v>439.0361872693334</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1100096212990704</v>
+        <v>0.1105563751509081</v>
       </c>
       <c r="T10">
-        <v>1.082666460031785</v>
+        <v>1.091885515452165</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2273,7 +2273,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>35.38860623501851</v>
+        <v>31.45653887557202</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2281,22 +2281,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1040468213873263</v>
+        <v>0.1038265511795079</v>
       </c>
       <c r="C11">
-        <v>2097.604617176369</v>
+        <v>2077.981910922782</v>
       </c>
       <c r="D11">
-        <v>1609.392617176369</v>
+        <v>1615.501910922783</v>
       </c>
       <c r="E11">
-        <v>-1861.712</v>
+        <v>-1835.98</v>
       </c>
       <c r="F11">
-        <v>231.588</v>
+        <v>257.32</v>
       </c>
       <c r="G11">
         <v>719.8</v>
@@ -2317,28 +2317,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M11">
-        <v>11.6488764</v>
+        <v>12.943196</v>
       </c>
       <c r="N11">
-        <v>354.7844569333334</v>
+        <v>353.4901373333334</v>
       </c>
       <c r="O11">
-        <v>85.14826966400001</v>
+        <v>84.83763296000001</v>
       </c>
       <c r="P11">
-        <v>269.6361872693334</v>
+        <v>268.6525043733334</v>
       </c>
       <c r="Q11">
-        <v>439.0361872693334</v>
+        <v>438.0525043733334</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1105563751509081</v>
+        <v>0.1111152790883421</v>
       </c>
       <c r="T11">
-        <v>1.091885515452165</v>
+        <v>1.101309438770777</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>31.45653887557202</v>
+        <v>28.31088498801482</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2363,22 +2363,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1038265511795079</v>
+        <v>0.1036062809716894</v>
       </c>
       <c r="C12">
-        <v>2077.981910922782</v>
+        <v>2058.405763464556</v>
       </c>
       <c r="D12">
-        <v>1615.501910922783</v>
+        <v>1621.657763464556</v>
       </c>
       <c r="E12">
-        <v>-1835.98</v>
+        <v>-1810.248</v>
       </c>
       <c r="F12">
-        <v>257.3200000000001</v>
+        <v>283.052</v>
       </c>
       <c r="G12">
         <v>719.8</v>
@@ -2399,28 +2399,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M12">
-        <v>12.943196</v>
+        <v>14.2375156</v>
       </c>
       <c r="N12">
-        <v>353.4901373333334</v>
+        <v>352.1958177333334</v>
       </c>
       <c r="O12">
-        <v>84.83763296000001</v>
+        <v>84.52699625600002</v>
       </c>
       <c r="P12">
-        <v>268.6525043733334</v>
+        <v>267.6688214773334</v>
       </c>
       <c r="Q12">
-        <v>438.0525043733334</v>
+        <v>437.0688214773334</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1111152790883421</v>
+        <v>0.1116867426648196</v>
       </c>
       <c r="T12">
-        <v>1.101309438770777</v>
+        <v>1.11094513564711</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>28.31088498801481</v>
+        <v>25.73716817092256</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1036062809716894</v>
+        <v>0.103386010763871</v>
       </c>
       <c r="C13">
-        <v>2058.405763464556</v>
+        <v>2038.876709072883</v>
       </c>
       <c r="D13">
-        <v>1621.657763464556</v>
+        <v>1627.860709072883</v>
       </c>
       <c r="E13">
-        <v>-1810.248</v>
+        <v>-1784.516</v>
       </c>
       <c r="F13">
-        <v>283.052</v>
+        <v>308.784</v>
       </c>
       <c r="G13">
         <v>719.8</v>
@@ -2481,28 +2481,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M13">
-        <v>14.2375156</v>
+        <v>15.5318352</v>
       </c>
       <c r="N13">
-        <v>352.1958177333334</v>
+        <v>350.9014981333334</v>
       </c>
       <c r="O13">
-        <v>84.52699625600002</v>
+        <v>84.21635955200001</v>
       </c>
       <c r="P13">
-        <v>267.6688214773334</v>
+        <v>266.6851385813334</v>
       </c>
       <c r="Q13">
-        <v>437.0688214773334</v>
+        <v>436.0851385813334</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1116867426648196</v>
+        <v>0.1122711940498534</v>
       </c>
       <c r="T13">
-        <v>1.11094513564711</v>
+        <v>1.120799825634268</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2519,7 +2519,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>25.73716817092256</v>
+        <v>23.59240415667901</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2527,22 +2527,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.103386010763871</v>
+        <v>0.1031657405560525</v>
       </c>
       <c r="C14">
-        <v>2038.876709072883</v>
+        <v>2019.395290224827</v>
       </c>
       <c r="D14">
-        <v>1627.860709072883</v>
+        <v>1634.111290224827</v>
       </c>
       <c r="E14">
-        <v>-1784.516</v>
+        <v>-1758.784</v>
       </c>
       <c r="F14">
-        <v>308.784</v>
+        <v>334.516</v>
       </c>
       <c r="G14">
         <v>719.8</v>
@@ -2563,28 +2563,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M14">
-        <v>15.5318352</v>
+        <v>16.8261548</v>
       </c>
       <c r="N14">
-        <v>350.9014981333334</v>
+        <v>349.6071785333334</v>
       </c>
       <c r="O14">
-        <v>84.21635955200001</v>
+        <v>83.90572284800001</v>
       </c>
       <c r="P14">
-        <v>266.6851385813334</v>
+        <v>265.7014556853334</v>
       </c>
       <c r="Q14">
-        <v>436.0851385813334</v>
+        <v>435.1014556853333</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1122711940498534</v>
+        <v>0.1128690810989109</v>
       </c>
       <c r="T14">
-        <v>1.120799825634268</v>
+        <v>1.130881060218833</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>23.59240415667901</v>
+        <v>21.77760383693447</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2609,22 +2609,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1031657405560525</v>
+        <v>0.102945470348234</v>
       </c>
       <c r="C15">
-        <v>2019.395290224827</v>
+        <v>1999.962057761482</v>
       </c>
       <c r="D15">
-        <v>1634.111290224827</v>
+        <v>1640.410057761482</v>
       </c>
       <c r="E15">
-        <v>-1758.784</v>
+        <v>-1733.052</v>
       </c>
       <c r="F15">
-        <v>334.516</v>
+        <v>360.248</v>
       </c>
       <c r="G15">
         <v>719.8</v>
@@ -2645,28 +2645,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M15">
-        <v>16.8261548</v>
+        <v>18.1204744</v>
       </c>
       <c r="N15">
-        <v>349.6071785333334</v>
+        <v>348.3128589333334</v>
       </c>
       <c r="O15">
-        <v>83.90572284800001</v>
+        <v>83.59508614400002</v>
       </c>
       <c r="P15">
-        <v>265.7014556853334</v>
+        <v>264.7177727893334</v>
       </c>
       <c r="Q15">
-        <v>435.1014556853333</v>
+        <v>434.1177727893333</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1128690810989109</v>
+        <v>0.1134808724979466</v>
       </c>
       <c r="T15">
-        <v>1.130881060218833</v>
+        <v>1.141196742119318</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>21.77760383693447</v>
+        <v>20.22206070572486</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2691,22 +2691,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.102945470348234</v>
+        <v>0.1027252001404156</v>
       </c>
       <c r="C16">
-        <v>1999.962057761482</v>
+        <v>1980.577571049785</v>
       </c>
       <c r="D16">
-        <v>1640.410057761482</v>
+        <v>1646.757571049785</v>
       </c>
       <c r="E16">
-        <v>-1733.052</v>
+        <v>-1707.32</v>
       </c>
       <c r="F16">
-        <v>360.248</v>
+        <v>385.9800000000001</v>
       </c>
       <c r="G16">
         <v>719.8</v>
@@ -2727,28 +2727,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M16">
-        <v>18.1204744</v>
+        <v>19.414794</v>
       </c>
       <c r="N16">
-        <v>348.3128589333334</v>
+        <v>347.0185393333334</v>
       </c>
       <c r="O16">
-        <v>83.59508614400002</v>
+        <v>83.28444944</v>
       </c>
       <c r="P16">
-        <v>264.7177727893334</v>
+        <v>263.7340898933334</v>
       </c>
       <c r="Q16">
-        <v>434.1177727893333</v>
+        <v>433.1340898933333</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1134808724979466</v>
+        <v>0.1141070589887242</v>
       </c>
       <c r="T16">
-        <v>1.141196742119318</v>
+        <v>1.151755145946873</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>20.22206070572486</v>
+        <v>18.8739233253432</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2773,22 +2773,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1027252001404156</v>
+        <v>0.1025049299325971</v>
       </c>
       <c r="C17">
-        <v>1980.577571049786</v>
+        <v>1961.242398148116</v>
       </c>
       <c r="D17">
-        <v>1646.757571049786</v>
+        <v>1653.154398148115</v>
       </c>
       <c r="E17">
-        <v>-1707.32</v>
+        <v>-1681.588</v>
       </c>
       <c r="F17">
-        <v>385.98</v>
+        <v>411.712</v>
       </c>
       <c r="G17">
         <v>719.8</v>
@@ -2809,28 +2809,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M17">
-        <v>19.414794</v>
+        <v>20.7091136</v>
       </c>
       <c r="N17">
-        <v>347.0185393333334</v>
+        <v>345.7242197333334</v>
       </c>
       <c r="O17">
-        <v>83.28444944</v>
+        <v>82.973812736</v>
       </c>
       <c r="P17">
-        <v>263.7340898933334</v>
+        <v>262.7504069973334</v>
       </c>
       <c r="Q17">
-        <v>433.1340898933333</v>
+        <v>432.1504069973333</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1141070589887242</v>
+        <v>0.1147481546816632</v>
       </c>
       <c r="T17">
-        <v>1.151755145946873</v>
+        <v>1.162564940341751</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2847,7 +2847,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>18.87392332534321</v>
+        <v>17.69430311750926</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2855,22 +2855,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1025049299325971</v>
+        <v>0.1022846597247787</v>
       </c>
       <c r="C18">
-        <v>1961.242398148116</v>
+        <v>1941.957115975758</v>
       </c>
       <c r="D18">
-        <v>1653.154398148115</v>
+        <v>1659.601115975758</v>
       </c>
       <c r="E18">
-        <v>-1681.588</v>
+        <v>-1655.856</v>
       </c>
       <c r="F18">
-        <v>411.712</v>
+        <v>437.4440000000001</v>
       </c>
       <c r="G18">
         <v>719.8</v>
@@ -2891,28 +2891,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M18">
-        <v>20.7091136</v>
+        <v>22.0034332</v>
       </c>
       <c r="N18">
-        <v>345.7242197333334</v>
+        <v>344.4299001333334</v>
       </c>
       <c r="O18">
-        <v>82.973812736</v>
+        <v>82.66317603200001</v>
       </c>
       <c r="P18">
-        <v>262.7504069973334</v>
+        <v>261.7667241013334</v>
       </c>
       <c r="Q18">
-        <v>432.1504069973333</v>
+        <v>431.1667241013333</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1147481546816632</v>
+        <v>0.1154046984635888</v>
       </c>
       <c r="T18">
-        <v>1.162564940341751</v>
+        <v>1.173635211709999</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2929,7 +2929,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>17.69430311750926</v>
+        <v>16.65346175765577</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2937,22 +2937,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1022846597247787</v>
+        <v>0.1020643895169602</v>
       </c>
       <c r="C19">
-        <v>1941.957115975758</v>
+        <v>1922.722310486356</v>
       </c>
       <c r="D19">
-        <v>1659.601115975758</v>
+        <v>1666.098310486356</v>
       </c>
       <c r="E19">
-        <v>-1655.856</v>
+        <v>-1630.124</v>
       </c>
       <c r="F19">
-        <v>437.4440000000001</v>
+        <v>463.1760000000001</v>
       </c>
       <c r="G19">
         <v>719.8</v>
@@ -2973,28 +2973,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M19">
-        <v>22.0034332</v>
+        <v>23.2977528</v>
       </c>
       <c r="N19">
-        <v>344.4299001333334</v>
+        <v>343.1355805333334</v>
       </c>
       <c r="O19">
-        <v>82.66317603200001</v>
+        <v>82.35253932800001</v>
       </c>
       <c r="P19">
-        <v>261.7667241013334</v>
+        <v>260.7830412053333</v>
       </c>
       <c r="Q19">
-        <v>431.1667241013333</v>
+        <v>430.1830412053333</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1154046984635888</v>
+        <v>0.116077255508488</v>
       </c>
       <c r="T19">
-        <v>1.173635211709999</v>
+        <v>1.184975489696986</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -3011,7 +3011,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>16.65346175765577</v>
+        <v>15.728269437786</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3019,22 +3019,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1020643895169602</v>
+        <v>0.1018441193091417</v>
       </c>
       <c r="C20">
-        <v>1922.722310486356</v>
+        <v>1903.538576845445</v>
       </c>
       <c r="D20">
-        <v>1666.098310486356</v>
+        <v>1672.646576845445</v>
       </c>
       <c r="E20">
-        <v>-1630.124</v>
+        <v>-1604.392</v>
       </c>
       <c r="F20">
-        <v>463.176</v>
+        <v>488.9080000000001</v>
       </c>
       <c r="G20">
         <v>719.8</v>
@@ -3055,28 +3055,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M20">
-        <v>23.2977528</v>
+        <v>24.5920724</v>
       </c>
       <c r="N20">
-        <v>343.1355805333334</v>
+        <v>341.8412609333334</v>
       </c>
       <c r="O20">
-        <v>82.35253932800001</v>
+        <v>82.04190262400002</v>
       </c>
       <c r="P20">
-        <v>260.7830412053333</v>
+        <v>259.7993583093333</v>
       </c>
       <c r="Q20">
-        <v>430.1830412053333</v>
+        <v>429.1993583093333</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.116077255508488</v>
+        <v>0.116766418900175</v>
       </c>
       <c r="T20">
-        <v>1.184975489696985</v>
+        <v>1.196595774547848</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>15.72826943778601</v>
+        <v>14.90046578316569</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3101,22 +3101,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1018441193091417</v>
+        <v>0.1016238491013233</v>
       </c>
       <c r="C21">
-        <v>1903.538576845445</v>
+        <v>1884.406519612198</v>
       </c>
       <c r="D21">
-        <v>1672.646576845445</v>
+        <v>1679.246519612198</v>
       </c>
       <c r="E21">
-        <v>-1604.392</v>
+        <v>-1578.66</v>
       </c>
       <c r="F21">
-        <v>488.9080000000001</v>
+        <v>514.6400000000001</v>
       </c>
       <c r="G21">
         <v>719.8</v>
@@ -3137,28 +3137,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M21">
-        <v>24.5920724</v>
+        <v>25.886392</v>
       </c>
       <c r="N21">
-        <v>341.8412609333334</v>
+        <v>340.5469413333334</v>
       </c>
       <c r="O21">
-        <v>82.04190262400002</v>
+        <v>81.73126592000001</v>
       </c>
       <c r="P21">
-        <v>259.7993583093333</v>
+        <v>258.8156754133334</v>
       </c>
       <c r="Q21">
-        <v>429.1993583093333</v>
+        <v>428.2156754133334</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.116766418900175</v>
+        <v>0.1174728113766541</v>
       </c>
       <c r="T21">
-        <v>1.196595774547848</v>
+        <v>1.208506566519981</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3175,7 +3175,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>14.90046578316569</v>
+        <v>14.1554424940074</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3183,22 +3183,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1016238491013233</v>
+        <v>0.1014035788935048</v>
       </c>
       <c r="C22">
-        <v>1884.406519612198</v>
+        <v>1865.326752925486</v>
       </c>
       <c r="D22">
-        <v>1679.246519612198</v>
+        <v>1685.898752925486</v>
       </c>
       <c r="E22">
-        <v>-1578.66</v>
+        <v>-1552.928</v>
       </c>
       <c r="F22">
-        <v>514.6400000000001</v>
+        <v>540.3720000000001</v>
       </c>
       <c r="G22">
         <v>719.8</v>
@@ -3219,28 +3219,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M22">
-        <v>25.886392</v>
+        <v>27.1807116</v>
       </c>
       <c r="N22">
-        <v>340.5469413333334</v>
+        <v>339.2526217333334</v>
       </c>
       <c r="O22">
-        <v>81.73126592000001</v>
+        <v>81.42062921600001</v>
       </c>
       <c r="P22">
-        <v>258.8156754133334</v>
+        <v>257.8319925173334</v>
       </c>
       <c r="Q22">
-        <v>428.2156754133334</v>
+        <v>427.2319925173334</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1174728113766541</v>
+        <v>0.1181970872069681</v>
       </c>
       <c r="T22">
-        <v>1.208506566519981</v>
+        <v>1.220718897529385</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3257,7 +3257,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>14.1554424940074</v>
+        <v>13.48137380381658</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3265,22 +3265,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1014035788935048</v>
+        <v>0.1014341086856863</v>
       </c>
       <c r="C23">
-        <v>1865.326752925486</v>
+        <v>1838.669598559183</v>
       </c>
       <c r="D23">
-        <v>1685.898752925486</v>
+        <v>1684.973598559184</v>
       </c>
       <c r="E23">
-        <v>-1552.928</v>
+        <v>-1527.196</v>
       </c>
       <c r="F23">
-        <v>540.3720000000001</v>
+        <v>566.104</v>
       </c>
       <c r="G23">
         <v>719.8</v>
@@ -3301,45 +3301,45 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M23">
-        <v>27.1807116</v>
+        <v>29.3241872</v>
       </c>
       <c r="N23">
-        <v>339.2526217333334</v>
+        <v>337.1091461333334</v>
       </c>
       <c r="O23">
-        <v>81.42062921600001</v>
+        <v>80.90619507200002</v>
       </c>
       <c r="P23">
-        <v>257.8319925173334</v>
+        <v>256.2029510613334</v>
       </c>
       <c r="Q23">
-        <v>427.2319925173334</v>
+        <v>425.6029510613334</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1181970872069681</v>
+        <v>0.1189399342124184</v>
       </c>
       <c r="T23">
-        <v>1.220718897529385</v>
+        <v>1.233244365231337</v>
       </c>
       <c r="U23">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V23">
         <v>0.24</v>
       </c>
       <c r="W23">
-        <v>0.038228</v>
+        <v>0.039368</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y23">
-        <v>13.48137380381658</v>
+        <v>12.49594168916414</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3347,22 +3347,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1014341086856863</v>
+        <v>0.1012252384778679</v>
       </c>
       <c r="C24">
-        <v>1838.669598559183</v>
+        <v>1819.287427542602</v>
       </c>
       <c r="D24">
-        <v>1684.973598559184</v>
+        <v>1691.323427542602</v>
       </c>
       <c r="E24">
-        <v>-1527.196</v>
+        <v>-1501.464</v>
       </c>
       <c r="F24">
-        <v>566.104</v>
+        <v>591.8360000000001</v>
       </c>
       <c r="G24">
         <v>719.8</v>
@@ -3383,28 +3383,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M24">
-        <v>29.3241872</v>
+        <v>30.65710480000001</v>
       </c>
       <c r="N24">
-        <v>337.1091461333334</v>
+        <v>335.7762285333334</v>
       </c>
       <c r="O24">
-        <v>80.90619507200002</v>
+        <v>80.58629484800001</v>
       </c>
       <c r="P24">
-        <v>256.2029510613334</v>
+        <v>255.1899336853334</v>
       </c>
       <c r="Q24">
-        <v>425.6029510613334</v>
+        <v>424.5899336853333</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1189399342124184</v>
+        <v>0.119702075945283</v>
       </c>
       <c r="T24">
-        <v>1.233244365231337</v>
+        <v>1.246095169756716</v>
       </c>
       <c r="U24">
         <v>0.0518</v>
@@ -3421,7 +3421,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>12.49594168916414</v>
+        <v>11.95263987659178</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3429,22 +3429,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1012252384778679</v>
+        <v>0.1010163682700494</v>
       </c>
       <c r="C25">
-        <v>1819.287427542602</v>
+        <v>1799.953296270066</v>
       </c>
       <c r="D25">
-        <v>1691.323427542602</v>
+        <v>1697.721296270066</v>
       </c>
       <c r="E25">
-        <v>-1501.464</v>
+        <v>-1475.732</v>
       </c>
       <c r="F25">
-        <v>591.8360000000001</v>
+        <v>617.5680000000001</v>
       </c>
       <c r="G25">
         <v>719.8</v>
@@ -3465,28 +3465,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M25">
-        <v>30.65710480000001</v>
+        <v>31.9900224</v>
       </c>
       <c r="N25">
-        <v>335.7762285333334</v>
+        <v>334.4433109333334</v>
       </c>
       <c r="O25">
-        <v>80.58629484800001</v>
+        <v>80.26639462400001</v>
       </c>
       <c r="P25">
-        <v>255.1899336853334</v>
+        <v>254.1769163093334</v>
       </c>
       <c r="Q25">
-        <v>424.5899336853333</v>
+        <v>423.5769163093334</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.119702075945283</v>
+        <v>0.1204842740395387</v>
       </c>
       <c r="T25">
-        <v>1.246095169756716</v>
+        <v>1.259284153348552</v>
       </c>
       <c r="U25">
         <v>0.0518</v>
@@ -3503,7 +3503,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>11.95263987659178</v>
+        <v>11.45461321506713</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1010163682700494</v>
+        <v>0.100807498062231</v>
       </c>
       <c r="C26">
-        <v>1799.953296270066</v>
+        <v>1780.66775197995</v>
       </c>
       <c r="D26">
-        <v>1697.721296270066</v>
+        <v>1704.16775197995</v>
       </c>
       <c r="E26">
-        <v>-1475.732</v>
+        <v>-1450</v>
       </c>
       <c r="F26">
-        <v>617.5680000000001</v>
+        <v>643.3000000000001</v>
       </c>
       <c r="G26">
         <v>719.8</v>
@@ -3547,28 +3547,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M26">
-        <v>31.9900224</v>
+        <v>33.32294</v>
       </c>
       <c r="N26">
-        <v>334.4433109333334</v>
+        <v>333.1103933333334</v>
       </c>
       <c r="O26">
-        <v>80.26639462400001</v>
+        <v>79.94649440000001</v>
       </c>
       <c r="P26">
-        <v>254.1769163093334</v>
+        <v>253.1638989333334</v>
       </c>
       <c r="Q26">
-        <v>423.5769163093334</v>
+        <v>422.5638989333333</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1204842740395387</v>
+        <v>0.1212873307496413</v>
       </c>
       <c r="T26">
-        <v>1.259284153348552</v>
+        <v>1.272824843169504</v>
       </c>
       <c r="U26">
         <v>0.0518</v>
@@ -3585,7 +3585,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>11.45461321506713</v>
+        <v>10.99642868646444</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3593,22 +3593,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.100807498062231</v>
+        <v>0.1005986278544125</v>
       </c>
       <c r="C27">
-        <v>1780.66775197995</v>
+        <v>1761.43135025404</v>
       </c>
       <c r="D27">
-        <v>1704.16775197995</v>
+        <v>1710.66335025404</v>
       </c>
       <c r="E27">
-        <v>-1450</v>
+        <v>-1424.268</v>
       </c>
       <c r="F27">
-        <v>643.3000000000001</v>
+        <v>669.032</v>
       </c>
       <c r="G27">
         <v>719.8</v>
@@ -3629,28 +3629,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M27">
-        <v>33.32294</v>
+        <v>34.6558576</v>
       </c>
       <c r="N27">
-        <v>333.1103933333334</v>
+        <v>331.7774757333334</v>
       </c>
       <c r="O27">
-        <v>79.94649440000001</v>
+        <v>79.62659417600001</v>
       </c>
       <c r="P27">
-        <v>253.1638989333334</v>
+        <v>252.1508815573334</v>
       </c>
       <c r="Q27">
-        <v>422.5638989333333</v>
+        <v>421.5508815573334</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1212873307496413</v>
+        <v>0.122112091695152</v>
       </c>
       <c r="T27">
-        <v>1.272824843169504</v>
+        <v>1.286731497580212</v>
       </c>
       <c r="U27">
         <v>0.0518</v>
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>10.99642868646444</v>
+        <v>10.57348912160042</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3675,22 +3675,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1005986278544125</v>
+        <v>0.100389757646594</v>
       </c>
       <c r="C28">
-        <v>1761.43135025404</v>
+        <v>1742.244655177138</v>
       </c>
       <c r="D28">
-        <v>1710.66335025404</v>
+        <v>1717.208655177139</v>
       </c>
       <c r="E28">
-        <v>-1424.268</v>
+        <v>-1398.536</v>
       </c>
       <c r="F28">
-        <v>669.032</v>
+        <v>694.7640000000001</v>
       </c>
       <c r="G28">
         <v>719.8</v>
@@ -3711,28 +3711,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M28">
-        <v>34.6558576</v>
+        <v>35.98877520000001</v>
       </c>
       <c r="N28">
-        <v>331.7774757333334</v>
+        <v>330.4445581333334</v>
       </c>
       <c r="O28">
-        <v>79.62659417600001</v>
+        <v>79.306693952</v>
       </c>
       <c r="P28">
-        <v>252.1508815573334</v>
+        <v>251.1378641813334</v>
       </c>
       <c r="Q28">
-        <v>421.5508815573334</v>
+        <v>420.5378641813334</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.122112091695152</v>
+        <v>0.1229594488309507</v>
       </c>
       <c r="T28">
-        <v>1.286731497580212</v>
+        <v>1.30101915622135</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3749,7 +3749,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>10.57348912160042</v>
+        <v>10.181878413393</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3757,22 +3757,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.100389757646594</v>
+        <v>0.1001808874387756</v>
       </c>
       <c r="C29">
-        <v>1742.244655177138</v>
+        <v>1723.108239500369</v>
       </c>
       <c r="D29">
-        <v>1717.208655177139</v>
+        <v>1723.804239500369</v>
       </c>
       <c r="E29">
-        <v>-1398.536</v>
+        <v>-1372.804</v>
       </c>
       <c r="F29">
-        <v>694.7640000000001</v>
+        <v>720.4960000000001</v>
       </c>
       <c r="G29">
         <v>719.8</v>
@@ -3793,28 +3793,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M29">
-        <v>35.98877520000001</v>
+        <v>37.3216928</v>
       </c>
       <c r="N29">
-        <v>330.4445581333334</v>
+        <v>329.1116405333334</v>
       </c>
       <c r="O29">
-        <v>79.306693952</v>
+        <v>78.98679372800001</v>
       </c>
       <c r="P29">
-        <v>251.1378641813334</v>
+        <v>250.1248468053334</v>
       </c>
       <c r="Q29">
-        <v>420.5378641813334</v>
+        <v>419.5248468053334</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1229594488309507</v>
+        <v>0.1238303436649661</v>
       </c>
       <c r="T29">
-        <v>1.30101915622135</v>
+        <v>1.315703694269186</v>
       </c>
       <c r="U29">
         <v>0.0518</v>
@@ -3831,7 +3831,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>10.181878413393</v>
+        <v>9.818239898628965</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3839,22 +3839,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1001808874387756</v>
+        <v>0.1003466972309571</v>
       </c>
       <c r="C30">
-        <v>1723.108239500369</v>
+        <v>1692.136259130833</v>
       </c>
       <c r="D30">
-        <v>1723.804239500369</v>
+        <v>1718.564259130833</v>
       </c>
       <c r="E30">
-        <v>-1372.804</v>
+        <v>-1347.072</v>
       </c>
       <c r="F30">
-        <v>720.4960000000001</v>
+        <v>746.2280000000002</v>
       </c>
       <c r="G30">
         <v>719.8</v>
@@ -3875,45 +3875,45 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M30">
-        <v>37.3216928</v>
+        <v>39.92319800000001</v>
       </c>
       <c r="N30">
-        <v>329.1116405333334</v>
+        <v>326.5101353333334</v>
       </c>
       <c r="O30">
-        <v>78.98679372800001</v>
+        <v>78.36243248000001</v>
       </c>
       <c r="P30">
-        <v>250.1248468053334</v>
+        <v>248.1477028533334</v>
       </c>
       <c r="Q30">
-        <v>419.5248468053334</v>
+        <v>417.5477028533334</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1238303436649661</v>
+        <v>0.1247257707478269</v>
       </c>
       <c r="T30">
-        <v>1.315703694269186</v>
+        <v>1.330801881276117</v>
       </c>
       <c r="U30">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V30">
         <v>0.24</v>
       </c>
       <c r="W30">
-        <v>0.039368</v>
+        <v>0.04066</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y30">
-        <v>9.818239898628965</v>
+        <v>9.178456428599064</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3921,22 +3921,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1003466972309571</v>
+        <v>0.1001507470231386</v>
       </c>
       <c r="C31">
-        <v>1692.136259130833</v>
+        <v>1672.600181766132</v>
       </c>
       <c r="D31">
-        <v>1718.564259130833</v>
+        <v>1724.760181766132</v>
       </c>
       <c r="E31">
-        <v>-1347.072</v>
+        <v>-1321.34</v>
       </c>
       <c r="F31">
-        <v>746.2280000000001</v>
+        <v>771.96</v>
       </c>
       <c r="G31">
         <v>719.8</v>
@@ -3957,28 +3957,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M31">
-        <v>39.923198</v>
+        <v>41.29986</v>
       </c>
       <c r="N31">
-        <v>326.5101353333334</v>
+        <v>325.1334733333334</v>
       </c>
       <c r="O31">
-        <v>78.36243248000001</v>
+        <v>78.03203360000001</v>
       </c>
       <c r="P31">
-        <v>248.1477028533334</v>
+        <v>247.1014397333334</v>
       </c>
       <c r="Q31">
-        <v>417.5477028533334</v>
+        <v>416.5014397333334</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1247257707478269</v>
+        <v>0.1256467814616266</v>
       </c>
       <c r="T31">
-        <v>1.330801881276117</v>
+        <v>1.346331445054673</v>
       </c>
       <c r="U31">
         <v>0.0535</v>
@@ -3995,7 +3995,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>9.178456428599066</v>
+        <v>8.872507880979096</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4003,22 +4003,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1001507470231386</v>
+        <v>0.09995479681532018</v>
       </c>
       <c r="C32">
-        <v>1672.600181766132</v>
+        <v>1653.108942251424</v>
       </c>
       <c r="D32">
-        <v>1724.760181766132</v>
+        <v>1731.000942251424</v>
       </c>
       <c r="E32">
-        <v>-1321.34</v>
+        <v>-1295.608</v>
       </c>
       <c r="F32">
-        <v>771.96</v>
+        <v>797.6920000000001</v>
       </c>
       <c r="G32">
         <v>719.8</v>
@@ -4039,28 +4039,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M32">
-        <v>41.29986</v>
+        <v>42.67652200000001</v>
       </c>
       <c r="N32">
-        <v>325.1334733333334</v>
+        <v>323.7568113333334</v>
       </c>
       <c r="O32">
-        <v>78.03203360000001</v>
+        <v>77.70163472000002</v>
       </c>
       <c r="P32">
-        <v>247.1014397333334</v>
+        <v>246.0551766133334</v>
       </c>
       <c r="Q32">
-        <v>416.5014397333334</v>
+        <v>415.4551766133334</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1256467814616266</v>
+        <v>0.1265944881381452</v>
       </c>
       <c r="T32">
-        <v>1.346331445054673</v>
+        <v>1.362311141116667</v>
       </c>
       <c r="U32">
         <v>0.0535</v>
@@ -4077,7 +4077,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>8.872507880979096</v>
+        <v>8.586297949334611</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4085,22 +4085,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09995479681532018</v>
+        <v>0.09975884660750173</v>
       </c>
       <c r="C33">
-        <v>1653.108942251424</v>
+        <v>1633.663029069317</v>
       </c>
       <c r="D33">
-        <v>1731.000942251424</v>
+        <v>1737.287029069317</v>
       </c>
       <c r="E33">
-        <v>-1295.608</v>
+        <v>-1269.876</v>
       </c>
       <c r="F33">
-        <v>797.6920000000001</v>
+        <v>823.4240000000001</v>
       </c>
       <c r="G33">
         <v>719.8</v>
@@ -4121,28 +4121,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M33">
-        <v>42.67652200000001</v>
+        <v>44.053184</v>
       </c>
       <c r="N33">
-        <v>323.7568113333334</v>
+        <v>322.3801493333334</v>
       </c>
       <c r="O33">
-        <v>77.70163472000002</v>
+        <v>77.37123584000001</v>
       </c>
       <c r="P33">
-        <v>246.0551766133334</v>
+        <v>245.0089134933334</v>
       </c>
       <c r="Q33">
-        <v>415.4551766133334</v>
+        <v>414.4089134933334</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1265944881381452</v>
+        <v>0.1275700685404437</v>
       </c>
       <c r="T33">
-        <v>1.362311141116667</v>
+        <v>1.378760828239307</v>
       </c>
       <c r="U33">
         <v>0.0535</v>
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>8.586297949334611</v>
+        <v>8.317976138417905</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4167,22 +4167,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09975884660750173</v>
+        <v>0.09956289639968324</v>
       </c>
       <c r="C34">
-        <v>1633.663029069317</v>
+        <v>1614.262937823929</v>
       </c>
       <c r="D34">
-        <v>1737.287029069317</v>
+        <v>1743.618937823929</v>
       </c>
       <c r="E34">
-        <v>-1269.876</v>
+        <v>-1244.144</v>
       </c>
       <c r="F34">
-        <v>823.4240000000001</v>
+        <v>849.1560000000002</v>
       </c>
       <c r="G34">
         <v>719.8</v>
@@ -4203,28 +4203,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M34">
-        <v>44.053184</v>
+        <v>45.42984600000001</v>
       </c>
       <c r="N34">
-        <v>322.3801493333334</v>
+        <v>321.0034873333334</v>
       </c>
       <c r="O34">
-        <v>77.37123584000001</v>
+        <v>77.04083696000001</v>
       </c>
       <c r="P34">
-        <v>245.0089134933334</v>
+        <v>243.9626503733334</v>
       </c>
       <c r="Q34">
-        <v>414.4089134933334</v>
+        <v>413.3626503733334</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1275700685404437</v>
+        <v>0.1285747707457959</v>
       </c>
       <c r="T34">
-        <v>1.378760828239307</v>
+        <v>1.395701550798443</v>
       </c>
       <c r="U34">
         <v>0.0535</v>
@@ -4241,7 +4241,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>8.317976138417905</v>
+        <v>8.065916255435543</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4249,22 +4249,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09956289639968324</v>
+        <v>0.0993669461918648</v>
       </c>
       <c r="C35">
-        <v>1614.262937823929</v>
+        <v>1594.909171371143</v>
       </c>
       <c r="D35">
-        <v>1743.618937823929</v>
+        <v>1749.997171371143</v>
       </c>
       <c r="E35">
-        <v>-1244.144</v>
+        <v>-1218.412</v>
       </c>
       <c r="F35">
-        <v>849.1560000000002</v>
+        <v>874.8880000000001</v>
       </c>
       <c r="G35">
         <v>719.8</v>
@@ -4285,28 +4285,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M35">
-        <v>45.42984600000001</v>
+        <v>46.80650800000001</v>
       </c>
       <c r="N35">
-        <v>321.0034873333334</v>
+        <v>319.6268253333334</v>
       </c>
       <c r="O35">
-        <v>77.04083696000001</v>
+        <v>76.71043808</v>
       </c>
       <c r="P35">
-        <v>243.9626503733334</v>
+        <v>242.9163872533334</v>
       </c>
       <c r="Q35">
-        <v>413.3626503733334</v>
+        <v>412.3163872533333</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1285747707457959</v>
+        <v>0.1296099184725224</v>
       </c>
       <c r="T35">
-        <v>1.395701550798443</v>
+        <v>1.413155628586645</v>
       </c>
       <c r="U35">
         <v>0.0535</v>
@@ -4323,7 +4323,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>8.065916255435543</v>
+        <v>7.82868342439332</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4331,22 +4331,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.0993669461918648</v>
+        <v>0.09938379598404634</v>
       </c>
       <c r="C36">
-        <v>1594.909171371143</v>
+        <v>1568.626872757274</v>
       </c>
       <c r="D36">
-        <v>1749.997171371143</v>
+        <v>1749.446872757274</v>
       </c>
       <c r="E36">
-        <v>-1218.412</v>
+        <v>-1192.68</v>
       </c>
       <c r="F36">
-        <v>874.8880000000001</v>
+        <v>900.6200000000002</v>
       </c>
       <c r="G36">
         <v>719.8</v>
@@ -4367,45 +4367,45 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M36">
-        <v>46.80650800000001</v>
+        <v>48.90366600000002</v>
       </c>
       <c r="N36">
-        <v>319.6268253333334</v>
+        <v>317.5296673333334</v>
       </c>
       <c r="O36">
-        <v>76.71043808</v>
+        <v>76.20712016</v>
       </c>
       <c r="P36">
-        <v>242.9163872533334</v>
+        <v>241.3225471733334</v>
       </c>
       <c r="Q36">
-        <v>412.3163872533333</v>
+        <v>410.7225471733334</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1296099184725224</v>
+        <v>0.1306769168985328</v>
       </c>
       <c r="T36">
-        <v>1.413155628586645</v>
+        <v>1.431146754922176</v>
       </c>
       <c r="U36">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V36">
         <v>0.24</v>
       </c>
       <c r="W36">
-        <v>0.04066</v>
+        <v>0.041268</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y36">
-        <v>7.82868342439332</v>
+        <v>7.49296245670689</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4413,22 +4413,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09938379598404634</v>
+        <v>0.09919392577622788</v>
       </c>
       <c r="C37">
-        <v>1568.626872757274</v>
+        <v>1549.115951961861</v>
       </c>
       <c r="D37">
-        <v>1749.446872757274</v>
+        <v>1755.667951961861</v>
       </c>
       <c r="E37">
-        <v>-1192.68</v>
+        <v>-1166.948</v>
       </c>
       <c r="F37">
-        <v>900.6200000000002</v>
+        <v>926.3520000000002</v>
       </c>
       <c r="G37">
         <v>719.8</v>
@@ -4449,28 +4449,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M37">
-        <v>48.90366600000002</v>
+        <v>50.30091360000002</v>
       </c>
       <c r="N37">
-        <v>317.5296673333334</v>
+        <v>316.1324197333334</v>
       </c>
       <c r="O37">
-        <v>76.20712016</v>
+        <v>75.87178073600001</v>
       </c>
       <c r="P37">
-        <v>241.3225471733334</v>
+        <v>240.2606389973334</v>
       </c>
       <c r="Q37">
-        <v>410.7225471733334</v>
+        <v>409.6606389973334</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1306769168985328</v>
+        <v>0.1317772590253561</v>
       </c>
       <c r="T37">
-        <v>1.431146754922176</v>
+        <v>1.449700103955692</v>
       </c>
       <c r="U37">
         <v>0.0543</v>
@@ -4487,7 +4487,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>7.49296245670689</v>
+        <v>7.284824610687256</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4495,22 +4495,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09919392577622788</v>
+        <v>0.09900405556840942</v>
       </c>
       <c r="C38">
-        <v>1549.115951961861</v>
+        <v>1529.649433706398</v>
       </c>
       <c r="D38">
-        <v>1755.667951961861</v>
+        <v>1761.933433706399</v>
       </c>
       <c r="E38">
-        <v>-1166.948</v>
+        <v>-1141.216</v>
       </c>
       <c r="F38">
-        <v>926.3520000000001</v>
+        <v>952.0840000000001</v>
       </c>
       <c r="G38">
         <v>719.8</v>
@@ -4531,28 +4531,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M38">
-        <v>50.30091360000001</v>
+        <v>51.6981612</v>
       </c>
       <c r="N38">
-        <v>316.1324197333334</v>
+        <v>314.7351721333334</v>
       </c>
       <c r="O38">
-        <v>75.87178073600001</v>
+        <v>75.53644131200001</v>
       </c>
       <c r="P38">
-        <v>240.2606389973334</v>
+        <v>239.1987308213334</v>
       </c>
       <c r="Q38">
-        <v>409.6606389973334</v>
+        <v>408.5987308213333</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1317772590253561</v>
+        <v>0.1329125326482689</v>
       </c>
       <c r="T38">
-        <v>1.449700103955692</v>
+        <v>1.468842448196622</v>
       </c>
       <c r="U38">
         <v>0.0543</v>
@@ -4569,7 +4569,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>7.284824610687257</v>
+        <v>7.087937459047061</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09900405556840942</v>
+        <v>0.09881418536059096</v>
       </c>
       <c r="C39">
-        <v>1529.649433706398</v>
+        <v>1510.227795073732</v>
       </c>
       <c r="D39">
-        <v>1761.933433706399</v>
+        <v>1768.243795073732</v>
       </c>
       <c r="E39">
-        <v>-1141.216</v>
+        <v>-1115.484</v>
       </c>
       <c r="F39">
-        <v>952.0840000000001</v>
+        <v>977.8160000000001</v>
       </c>
       <c r="G39">
         <v>719.8</v>
@@ -4613,28 +4613,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M39">
-        <v>51.6981612</v>
+        <v>53.09540880000001</v>
       </c>
       <c r="N39">
-        <v>314.7351721333334</v>
+        <v>313.3379245333334</v>
       </c>
       <c r="O39">
-        <v>75.53644131200001</v>
+        <v>75.20110188800001</v>
       </c>
       <c r="P39">
-        <v>239.1987308213334</v>
+        <v>238.1368226453334</v>
       </c>
       <c r="Q39">
-        <v>408.5987308213333</v>
+        <v>407.5368226453334</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1329125326482689</v>
+        <v>0.1340844280009532</v>
       </c>
       <c r="T39">
-        <v>1.468842448196622</v>
+        <v>1.488602287413065</v>
       </c>
       <c r="U39">
         <v>0.0543</v>
@@ -4651,7 +4651,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>7.087937459047061</v>
+        <v>6.901412789072138</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4659,22 +4659,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09881418536059096</v>
+        <v>0.09862431515277249</v>
       </c>
       <c r="C40">
-        <v>1510.227795073732</v>
+        <v>1490.85152000596</v>
       </c>
       <c r="D40">
-        <v>1768.243795073732</v>
+        <v>1774.59952000596</v>
       </c>
       <c r="E40">
-        <v>-1115.484</v>
+        <v>-1089.752</v>
       </c>
       <c r="F40">
-        <v>977.8160000000001</v>
+        <v>1003.548</v>
       </c>
       <c r="G40">
         <v>719.8</v>
@@ -4695,28 +4695,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M40">
-        <v>53.09540880000001</v>
+        <v>54.49265640000001</v>
       </c>
       <c r="N40">
-        <v>313.3379245333334</v>
+        <v>311.9406769333334</v>
       </c>
       <c r="O40">
-        <v>75.20110188800001</v>
+        <v>74.86576246400001</v>
       </c>
       <c r="P40">
-        <v>238.1368226453334</v>
+        <v>237.0749144693334</v>
       </c>
       <c r="Q40">
-        <v>407.5368226453334</v>
+        <v>406.4749144693334</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1340844280009532</v>
+        <v>0.1352947461520861</v>
       </c>
       <c r="T40">
-        <v>1.488602287413065</v>
+        <v>1.509009990210375</v>
       </c>
       <c r="U40">
         <v>0.0543</v>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>6.901412789072138</v>
+        <v>6.724453486788238</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4741,22 +4741,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09862431515277249</v>
+        <v>0.09843444494495403</v>
       </c>
       <c r="C41">
-        <v>1490.85152000596</v>
+        <v>1471.521099428151</v>
       </c>
       <c r="D41">
-        <v>1774.59952000596</v>
+        <v>1781.001099428152</v>
       </c>
       <c r="E41">
-        <v>-1089.752</v>
+        <v>-1064.02</v>
       </c>
       <c r="F41">
-        <v>1003.548</v>
+        <v>1029.28</v>
       </c>
       <c r="G41">
         <v>719.8</v>
@@ -4777,28 +4777,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M41">
-        <v>54.49265640000001</v>
+        <v>55.88990400000001</v>
       </c>
       <c r="N41">
-        <v>311.9406769333334</v>
+        <v>310.5434293333334</v>
       </c>
       <c r="O41">
-        <v>74.86576246400001</v>
+        <v>74.53042304000002</v>
       </c>
       <c r="P41">
-        <v>237.0749144693334</v>
+        <v>236.0130062933334</v>
       </c>
       <c r="Q41">
-        <v>406.4749144693334</v>
+        <v>405.4130062933334</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1352947461520861</v>
+        <v>0.1365454082415901</v>
       </c>
       <c r="T41">
-        <v>1.509009990210375</v>
+        <v>1.530097949767596</v>
       </c>
       <c r="U41">
         <v>0.0543</v>
@@ -4815,7 +4815,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>6.724453486788238</v>
+        <v>6.556342149618531</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4823,22 +4823,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09843444494495403</v>
+        <v>0.09824457473713556</v>
       </c>
       <c r="C42">
-        <v>1471.521099428151</v>
+        <v>1452.23703137475</v>
       </c>
       <c r="D42">
-        <v>1781.001099428152</v>
+        <v>1787.44903137475</v>
       </c>
       <c r="E42">
-        <v>-1064.02</v>
+        <v>-1038.288</v>
       </c>
       <c r="F42">
-        <v>1029.28</v>
+        <v>1055.012</v>
       </c>
       <c r="G42">
         <v>719.8</v>
@@ -4859,28 +4859,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M42">
-        <v>55.88990400000001</v>
+        <v>57.28715160000001</v>
       </c>
       <c r="N42">
-        <v>310.5434293333334</v>
+        <v>309.1461817333334</v>
       </c>
       <c r="O42">
-        <v>74.53042304000002</v>
+        <v>74.19508361600001</v>
       </c>
       <c r="P42">
-        <v>236.0130062933334</v>
+        <v>234.9510981173334</v>
       </c>
       <c r="Q42">
-        <v>405.4130062933334</v>
+        <v>404.3510981173334</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1365454082415901</v>
+        <v>0.137838465656162</v>
       </c>
       <c r="T42">
-        <v>1.530097949767596</v>
+        <v>1.551900755411502</v>
       </c>
       <c r="U42">
         <v>0.0543</v>
@@ -4897,7 +4897,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>6.556342149618531</v>
+        <v>6.396431365481494</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4905,22 +4905,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09824457473713556</v>
+        <v>0.0980547045293171</v>
       </c>
       <c r="C43">
-        <v>1452.23703137475</v>
+        <v>1432.999821118736</v>
       </c>
       <c r="D43">
-        <v>1787.44903137475</v>
+        <v>1793.943821118736</v>
       </c>
       <c r="E43">
-        <v>-1038.288</v>
+        <v>-1012.556</v>
       </c>
       <c r="F43">
-        <v>1055.012</v>
+        <v>1080.744</v>
       </c>
       <c r="G43">
         <v>719.8</v>
@@ -4941,28 +4941,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M43">
-        <v>57.28715160000001</v>
+        <v>58.68439920000001</v>
       </c>
       <c r="N43">
-        <v>309.1461817333334</v>
+        <v>307.7489341333334</v>
       </c>
       <c r="O43">
-        <v>74.19508361600001</v>
+        <v>73.85974419200001</v>
       </c>
       <c r="P43">
-        <v>234.9510981173334</v>
+        <v>233.8891899413334</v>
       </c>
       <c r="Q43">
-        <v>404.3510981173334</v>
+        <v>403.2891899413333</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.137838465656162</v>
+        <v>0.1391761112574433</v>
       </c>
       <c r="T43">
-        <v>1.551900755411502</v>
+        <v>1.57445538193968</v>
       </c>
       <c r="U43">
         <v>0.0543</v>
@@ -4979,7 +4979,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>6.396431365481494</v>
+        <v>6.244135380589077</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4987,22 +4987,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09805470452931711</v>
+        <v>0.09819163432149865</v>
       </c>
       <c r="C44">
-        <v>1432.999821118735</v>
+        <v>1402.579203216424</v>
       </c>
       <c r="D44">
-        <v>1793.943821118736</v>
+        <v>1789.255203216424</v>
       </c>
       <c r="E44">
-        <v>-1012.556</v>
+        <v>-986.8240000000001</v>
       </c>
       <c r="F44">
-        <v>1080.744</v>
+        <v>1106.476</v>
       </c>
       <c r="G44">
         <v>719.8</v>
@@ -5023,45 +5023,45 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M44">
-        <v>58.68439920000001</v>
+        <v>61.18812280000001</v>
       </c>
       <c r="N44">
-        <v>307.7489341333334</v>
+        <v>305.2452105333334</v>
       </c>
       <c r="O44">
-        <v>73.85974419200001</v>
+        <v>73.25885052800001</v>
       </c>
       <c r="P44">
-        <v>233.8891899413334</v>
+        <v>231.9863600053334</v>
       </c>
       <c r="Q44">
-        <v>403.2891899413333</v>
+        <v>401.3863600053334</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1391761112574433</v>
+        <v>0.1405606917921029</v>
       </c>
       <c r="T44">
-        <v>1.57445538193968</v>
+        <v>1.597801398872357</v>
       </c>
       <c r="U44">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V44">
         <v>0.24</v>
       </c>
       <c r="W44">
-        <v>0.041268</v>
+        <v>0.042028</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y44">
-        <v>6.244135380589077</v>
+        <v>5.988634992628558</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5069,22 +5069,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09819163432149865</v>
+        <v>0.09800936411368019</v>
       </c>
       <c r="C45">
-        <v>1402.579203216424</v>
+        <v>1383.093743913997</v>
       </c>
       <c r="D45">
-        <v>1789.255203216424</v>
+        <v>1795.501743913997</v>
       </c>
       <c r="E45">
-        <v>-986.8240000000001</v>
+        <v>-961.0920000000001</v>
       </c>
       <c r="F45">
-        <v>1106.476</v>
+        <v>1132.208</v>
       </c>
       <c r="G45">
         <v>719.8</v>
@@ -5105,28 +5105,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M45">
-        <v>61.18812280000001</v>
+        <v>62.61110240000001</v>
       </c>
       <c r="N45">
-        <v>305.2452105333334</v>
+        <v>303.8222309333334</v>
       </c>
       <c r="O45">
-        <v>73.25885052800001</v>
+        <v>72.91733542400002</v>
       </c>
       <c r="P45">
-        <v>231.9863600053334</v>
+        <v>230.9048955093334</v>
       </c>
       <c r="Q45">
-        <v>401.3863600053334</v>
+        <v>400.3048955093334</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1405606917921029</v>
+        <v>0.1419947216315718</v>
       </c>
       <c r="T45">
-        <v>1.597801398872357</v>
+        <v>1.621981202124057</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5143,7 +5143,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>5.988634992628558</v>
+        <v>5.852529651887001</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5151,22 +5151,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09800936411368019</v>
+        <v>0.09782709390586172</v>
       </c>
       <c r="C46">
-        <v>1383.093743913997</v>
+        <v>1363.652052509626</v>
       </c>
       <c r="D46">
-        <v>1795.501743913997</v>
+        <v>1801.792052509626</v>
       </c>
       <c r="E46">
-        <v>-961.0920000000001</v>
+        <v>-935.3600000000001</v>
       </c>
       <c r="F46">
-        <v>1132.208</v>
+        <v>1157.94</v>
       </c>
       <c r="G46">
         <v>719.8</v>
@@ -5187,28 +5187,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M46">
-        <v>62.61110240000001</v>
+        <v>64.03408200000001</v>
       </c>
       <c r="N46">
-        <v>303.8222309333334</v>
+        <v>302.3992513333334</v>
       </c>
       <c r="O46">
-        <v>72.91733542400002</v>
+        <v>72.57582032000001</v>
       </c>
       <c r="P46">
-        <v>230.9048955093334</v>
+        <v>229.8234310133334</v>
       </c>
       <c r="Q46">
-        <v>400.3048955093334</v>
+        <v>399.2234310133334</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1419947216315718</v>
+        <v>0.1434808980106577</v>
       </c>
       <c r="T46">
-        <v>1.621981202124057</v>
+        <v>1.647040270948546</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5225,7 +5225,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>5.852529651887001</v>
+        <v>5.722473437400622</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5233,22 +5233,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09782709390586172</v>
+        <v>0.09764482369804325</v>
       </c>
       <c r="C47">
-        <v>1363.652052509626</v>
+        <v>1344.25459062609</v>
       </c>
       <c r="D47">
-        <v>1801.792052509626</v>
+        <v>1808.12659062609</v>
       </c>
       <c r="E47">
-        <v>-935.3600000000001</v>
+        <v>-909.6279999999999</v>
       </c>
       <c r="F47">
-        <v>1157.94</v>
+        <v>1183.672</v>
       </c>
       <c r="G47">
         <v>719.8</v>
@@ -5269,28 +5269,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M47">
-        <v>64.03408200000001</v>
+        <v>65.45706160000002</v>
       </c>
       <c r="N47">
-        <v>302.3992513333334</v>
+        <v>300.9762717333334</v>
       </c>
       <c r="O47">
-        <v>72.57582032000001</v>
+        <v>72.23430521600001</v>
       </c>
       <c r="P47">
-        <v>229.8234310133334</v>
+        <v>228.7419665173334</v>
       </c>
       <c r="Q47">
-        <v>399.2234310133334</v>
+        <v>398.1419665173333</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1434808980106577</v>
+        <v>0.1450221179593394</v>
       </c>
       <c r="T47">
-        <v>1.647040270948546</v>
+        <v>1.673027453433202</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5307,7 +5307,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>5.722473437400622</v>
+        <v>5.598071840935391</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5315,22 +5315,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09764482369804325</v>
+        <v>0.0974625534902248</v>
       </c>
       <c r="C48">
-        <v>1344.25459062609</v>
+        <v>1324.901826400757</v>
       </c>
       <c r="D48">
-        <v>1808.12659062609</v>
+        <v>1814.505826400757</v>
       </c>
       <c r="E48">
-        <v>-909.6279999999999</v>
+        <v>-883.896</v>
       </c>
       <c r="F48">
-        <v>1183.672</v>
+        <v>1209.404</v>
       </c>
       <c r="G48">
         <v>719.8</v>
@@ -5351,28 +5351,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M48">
-        <v>65.45706160000002</v>
+        <v>66.88004120000001</v>
       </c>
       <c r="N48">
-        <v>300.9762717333334</v>
+        <v>299.5532921333334</v>
       </c>
       <c r="O48">
-        <v>72.23430521600001</v>
+        <v>71.89279011200001</v>
       </c>
       <c r="P48">
-        <v>228.7419665173334</v>
+        <v>227.6605020213334</v>
       </c>
       <c r="Q48">
-        <v>398.1419665173333</v>
+        <v>397.0605020213334</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1450221179593394</v>
+        <v>0.1466214971513675</v>
       </c>
       <c r="T48">
-        <v>1.673027453433202</v>
+        <v>1.699995284313505</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5389,7 +5389,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>5.598071840935391</v>
+        <v>5.478963929426128</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5397,22 +5397,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.0974625534902248</v>
+        <v>0.09728028328240633</v>
       </c>
       <c r="C49">
-        <v>1324.901826400757</v>
+        <v>1305.594234600913</v>
       </c>
       <c r="D49">
-        <v>1814.505826400757</v>
+        <v>1820.930234600913</v>
       </c>
       <c r="E49">
-        <v>-883.896</v>
+        <v>-858.164</v>
       </c>
       <c r="F49">
-        <v>1209.404</v>
+        <v>1235.136</v>
       </c>
       <c r="G49">
         <v>719.8</v>
@@ -5433,28 +5433,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M49">
-        <v>66.88004120000001</v>
+        <v>68.30302080000001</v>
       </c>
       <c r="N49">
-        <v>299.5532921333334</v>
+        <v>298.1303125333334</v>
       </c>
       <c r="O49">
-        <v>71.89279011200001</v>
+        <v>71.551275008</v>
       </c>
       <c r="P49">
-        <v>227.6605020213334</v>
+        <v>226.5790375253334</v>
       </c>
       <c r="Q49">
-        <v>397.0605020213334</v>
+        <v>395.9790375253334</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1466214971513675</v>
+        <v>0.1482823909277045</v>
       </c>
       <c r="T49">
-        <v>1.699995284313505</v>
+        <v>1.728000339458435</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5471,7 +5471,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>5.478963929426128</v>
+        <v>5.364818847563083</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5479,22 +5479,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09728028328240633</v>
+        <v>0.09709801307458786</v>
       </c>
       <c r="C50">
-        <v>1305.594234600913</v>
+        <v>1286.332296741547</v>
       </c>
       <c r="D50">
-        <v>1820.930234600913</v>
+        <v>1827.400296741547</v>
       </c>
       <c r="E50">
-        <v>-858.164</v>
+        <v>-832.432</v>
       </c>
       <c r="F50">
-        <v>1235.136</v>
+        <v>1260.868</v>
       </c>
       <c r="G50">
         <v>719.8</v>
@@ -5515,28 +5515,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M50">
-        <v>68.30302080000001</v>
+        <v>69.72600040000002</v>
       </c>
       <c r="N50">
-        <v>298.1303125333334</v>
+        <v>296.7073329333334</v>
       </c>
       <c r="O50">
-        <v>71.551275008</v>
+        <v>71.20975990400001</v>
       </c>
       <c r="P50">
-        <v>226.5790375253334</v>
+        <v>225.4975730293334</v>
       </c>
       <c r="Q50">
-        <v>395.9790375253334</v>
+        <v>394.8975730293333</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1482823909277045</v>
+        <v>0.1500084177933095</v>
       </c>
       <c r="T50">
-        <v>1.728000339458435</v>
+        <v>1.757103632060029</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5553,7 +5553,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>5.364818847563083</v>
+        <v>5.255332748633224</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5561,22 +5561,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09709801307458786</v>
+        <v>0.09691574286676942</v>
       </c>
       <c r="C51">
-        <v>1286.332296741547</v>
+        <v>1267.116501205654</v>
       </c>
       <c r="D51">
-        <v>1827.400296741547</v>
+        <v>1833.916501205654</v>
       </c>
       <c r="E51">
-        <v>-832.432</v>
+        <v>-806.7</v>
       </c>
       <c r="F51">
-        <v>1260.868</v>
+        <v>1286.6</v>
       </c>
       <c r="G51">
         <v>719.8</v>
@@ -5597,28 +5597,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M51">
-        <v>69.72600040000002</v>
+        <v>71.14898000000001</v>
       </c>
       <c r="N51">
-        <v>296.7073329333334</v>
+        <v>295.2843533333334</v>
       </c>
       <c r="O51">
-        <v>71.20975990400001</v>
+        <v>70.86824480000001</v>
       </c>
       <c r="P51">
-        <v>225.4975730293334</v>
+        <v>224.4161085333334</v>
       </c>
       <c r="Q51">
-        <v>394.8975730293333</v>
+        <v>393.8161085333334</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1500084177933095</v>
+        <v>0.1518034857335388</v>
       </c>
       <c r="T51">
-        <v>1.757103632060029</v>
+        <v>1.787371056365687</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5635,7 +5635,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>5.255332748633224</v>
+        <v>5.150226093660561</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09691574286676942</v>
+        <v>0.09673347265895095</v>
       </c>
       <c r="C52">
-        <v>1267.116501205654</v>
+        <v>1247.947343367128</v>
       </c>
       <c r="D52">
-        <v>1833.916501205654</v>
+        <v>1840.479343367128</v>
       </c>
       <c r="E52">
-        <v>-806.7</v>
+        <v>-780.9680000000001</v>
       </c>
       <c r="F52">
-        <v>1286.6</v>
+        <v>1312.332</v>
       </c>
       <c r="G52">
         <v>719.8</v>
@@ -5679,28 +5679,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M52">
-        <v>71.14898000000001</v>
+        <v>72.57195960000001</v>
       </c>
       <c r="N52">
-        <v>295.2843533333334</v>
+        <v>293.8613737333334</v>
       </c>
       <c r="O52">
-        <v>70.86824480000001</v>
+        <v>70.526729696</v>
       </c>
       <c r="P52">
-        <v>224.4161085333334</v>
+        <v>223.3346440373334</v>
       </c>
       <c r="Q52">
-        <v>393.8161085333334</v>
+        <v>392.7346440373334</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1518034857335388</v>
+        <v>0.1536718217529611</v>
       </c>
       <c r="T52">
-        <v>1.787371056365687</v>
+        <v>1.818873885745045</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5717,7 +5717,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>5.150226093660561</v>
+        <v>5.049241268294667</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5725,22 +5725,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09673347265895095</v>
+        <v>0.0965512024511325</v>
       </c>
       <c r="C53">
-        <v>1247.947343367128</v>
+        <v>1228.825325716298</v>
       </c>
       <c r="D53">
-        <v>1840.479343367128</v>
+        <v>1847.089325716298</v>
       </c>
       <c r="E53">
-        <v>-780.9680000000001</v>
+        <v>-755.2360000000001</v>
       </c>
       <c r="F53">
-        <v>1312.332</v>
+        <v>1338.064</v>
       </c>
       <c r="G53">
         <v>719.8</v>
@@ -5761,28 +5761,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M53">
-        <v>72.57195960000001</v>
+        <v>73.9949392</v>
       </c>
       <c r="N53">
-        <v>293.8613737333334</v>
+        <v>292.4383941333334</v>
       </c>
       <c r="O53">
-        <v>70.526729696</v>
+        <v>70.18521459200002</v>
       </c>
       <c r="P53">
-        <v>223.3346440373334</v>
+        <v>222.2531795413334</v>
       </c>
       <c r="Q53">
-        <v>392.7346440373334</v>
+        <v>391.6531795413334</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1536718217529611</v>
+        <v>0.155618005106526</v>
       </c>
       <c r="T53">
-        <v>1.818873885745045</v>
+        <v>1.85168933301521</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5799,7 +5799,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>5.049241268294667</v>
+        <v>4.952140474673616</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5807,22 +5807,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.0965512024511325</v>
+        <v>0.09636893224331403</v>
       </c>
       <c r="C54">
-        <v>1228.825325716298</v>
+        <v>1209.750957988177</v>
       </c>
       <c r="D54">
-        <v>1847.089325716298</v>
+        <v>1853.746957988177</v>
       </c>
       <c r="E54">
-        <v>-755.2360000000001</v>
+        <v>-729.5039999999999</v>
       </c>
       <c r="F54">
-        <v>1338.064</v>
+        <v>1363.796</v>
       </c>
       <c r="G54">
         <v>719.8</v>
@@ -5843,28 +5843,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M54">
-        <v>73.9949392</v>
+        <v>75.41791880000002</v>
       </c>
       <c r="N54">
-        <v>292.4383941333334</v>
+        <v>291.0154145333333</v>
       </c>
       <c r="O54">
-        <v>70.18521459200002</v>
+        <v>69.843699488</v>
       </c>
       <c r="P54">
-        <v>222.2531795413334</v>
+        <v>221.1717150453333</v>
       </c>
       <c r="Q54">
-        <v>391.6531795413334</v>
+        <v>390.5717150453333</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.155618005106526</v>
+        <v>0.1576470047730086</v>
       </c>
       <c r="T54">
-        <v>1.85168933301521</v>
+        <v>1.885901182296871</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5881,7 +5881,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>4.952140474673616</v>
+        <v>4.858703861943924</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5889,22 +5889,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09636893224331403</v>
+        <v>0.09618666203549556</v>
       </c>
       <c r="C55">
-        <v>1209.750957988177</v>
+        <v>1190.724757293504</v>
       </c>
       <c r="D55">
-        <v>1853.746957988177</v>
+        <v>1860.452757293504</v>
       </c>
       <c r="E55">
-        <v>-729.5039999999999</v>
+        <v>-703.7719999999999</v>
       </c>
       <c r="F55">
-        <v>1363.796</v>
+        <v>1389.528</v>
       </c>
       <c r="G55">
         <v>719.8</v>
@@ -5925,28 +5925,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M55">
-        <v>75.41791880000002</v>
+        <v>76.84089840000001</v>
       </c>
       <c r="N55">
-        <v>291.0154145333333</v>
+        <v>289.5924349333334</v>
       </c>
       <c r="O55">
-        <v>69.843699488</v>
+        <v>69.502184384</v>
       </c>
       <c r="P55">
-        <v>221.1717150453333</v>
+        <v>220.0902505493334</v>
       </c>
       <c r="Q55">
-        <v>390.5717150453333</v>
+        <v>389.4902505493334</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1576470047730086</v>
+        <v>0.1597642218162947</v>
       </c>
       <c r="T55">
-        <v>1.885901182296871</v>
+        <v>1.92160050328643</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5963,7 +5963,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>4.858703861943924</v>
+        <v>4.768727864500519</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5971,22 +5971,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09618666203549556</v>
+        <v>0.09600439182767712</v>
       </c>
       <c r="C56">
-        <v>1190.724757293504</v>
+        <v>1171.747248252626</v>
       </c>
       <c r="D56">
-        <v>1860.452757293504</v>
+        <v>1867.207248252627</v>
       </c>
       <c r="E56">
-        <v>-703.7719999999999</v>
+        <v>-678.04</v>
       </c>
       <c r="F56">
-        <v>1389.528</v>
+        <v>1415.26</v>
       </c>
       <c r="G56">
         <v>719.8</v>
@@ -6007,28 +6007,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M56">
-        <v>76.84089840000001</v>
+        <v>78.26387800000002</v>
       </c>
       <c r="N56">
-        <v>289.5924349333334</v>
+        <v>288.1694553333334</v>
       </c>
       <c r="O56">
-        <v>69.502184384</v>
+        <v>69.16066928000001</v>
       </c>
       <c r="P56">
-        <v>220.0902505493334</v>
+        <v>219.0087860533334</v>
       </c>
       <c r="Q56">
-        <v>389.4902505493334</v>
+        <v>388.4087860533334</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1597642218162947</v>
+        <v>0.161975537394838</v>
       </c>
       <c r="T56">
-        <v>1.92160050328643</v>
+        <v>1.958886460764415</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -6045,7 +6045,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>4.768727864500519</v>
+        <v>4.6820237215096</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6053,22 +6053,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09600439182767712</v>
+        <v>0.09582212161985863</v>
       </c>
       <c r="C57">
-        <v>1171.747248252626</v>
+        <v>1152.818963132326</v>
       </c>
       <c r="D57">
-        <v>1867.207248252627</v>
+        <v>1874.010963132326</v>
       </c>
       <c r="E57">
-        <v>-678.04</v>
+        <v>-652.308</v>
       </c>
       <c r="F57">
-        <v>1415.26</v>
+        <v>1440.992</v>
       </c>
       <c r="G57">
         <v>719.8</v>
@@ -6089,28 +6089,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M57">
-        <v>78.26387800000002</v>
+        <v>79.68685760000001</v>
       </c>
       <c r="N57">
-        <v>288.1694553333334</v>
+        <v>286.7464757333334</v>
       </c>
       <c r="O57">
-        <v>69.16066928000001</v>
+        <v>68.81915417600001</v>
       </c>
       <c r="P57">
-        <v>219.0087860533334</v>
+        <v>217.9273215573334</v>
       </c>
       <c r="Q57">
-        <v>388.4087860533334</v>
+        <v>387.3273215573334</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.161975537394838</v>
+        <v>0.1642873673178605</v>
       </c>
       <c r="T57">
-        <v>1.958886460764415</v>
+        <v>1.997867234491398</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -6127,7 +6127,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>4.6820237215096</v>
+        <v>4.598416155054072</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6135,22 +6135,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09582212161985863</v>
+        <v>0.09563985141204018</v>
       </c>
       <c r="C58">
-        <v>1152.818963132326</v>
+        <v>1133.940441985629</v>
       </c>
       <c r="D58">
-        <v>1874.010963132326</v>
+        <v>1880.86444198563</v>
       </c>
       <c r="E58">
-        <v>-652.308</v>
+        <v>-626.5759999999998</v>
       </c>
       <c r="F58">
-        <v>1440.992</v>
+        <v>1466.724</v>
       </c>
       <c r="G58">
         <v>719.8</v>
@@ -6171,28 +6171,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M58">
-        <v>79.68685760000001</v>
+        <v>81.10983720000003</v>
       </c>
       <c r="N58">
-        <v>286.7464757333334</v>
+        <v>285.3234961333334</v>
       </c>
       <c r="O58">
-        <v>68.81915417600001</v>
+        <v>68.477639072</v>
       </c>
       <c r="P58">
-        <v>217.9273215573334</v>
+        <v>216.8458570613334</v>
       </c>
       <c r="Q58">
-        <v>387.3273215573334</v>
+        <v>386.2458570613334</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1642873673178605</v>
+        <v>0.1667067242140469</v>
       </c>
       <c r="T58">
-        <v>1.997867234491398</v>
+        <v>2.038661067461498</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6209,7 +6209,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>4.598416155054072</v>
+        <v>4.517742187421543</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6217,22 +6217,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09563985141204018</v>
+        <v>0.0965595812042217</v>
       </c>
       <c r="C59">
-        <v>1133.940441985629</v>
+        <v>1074.128431447536</v>
       </c>
       <c r="D59">
-        <v>1880.86444198563</v>
+        <v>1846.784431447537</v>
       </c>
       <c r="E59">
-        <v>-626.5759999999998</v>
+        <v>-600.8439999999998</v>
       </c>
       <c r="F59">
-        <v>1466.724</v>
+        <v>1492.456</v>
       </c>
       <c r="G59">
         <v>719.8</v>
@@ -6253,45 +6253,45 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M59">
-        <v>81.10983720000003</v>
+        <v>86.26395680000003</v>
       </c>
       <c r="N59">
-        <v>285.3234961333334</v>
+        <v>280.1693765333334</v>
       </c>
       <c r="O59">
-        <v>68.477639072</v>
+        <v>67.240650368</v>
       </c>
       <c r="P59">
-        <v>216.8458570613334</v>
+        <v>212.9287261653334</v>
       </c>
       <c r="Q59">
-        <v>386.2458570613334</v>
+        <v>382.3287261653334</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1667067242140469</v>
+        <v>0.1692412885814803</v>
       </c>
       <c r="T59">
-        <v>2.038661067461498</v>
+        <v>2.081397463906363</v>
       </c>
       <c r="U59">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V59">
         <v>0.24</v>
       </c>
       <c r="W59">
-        <v>0.042028</v>
+        <v>0.043928</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y59">
-        <v>4.517742187421543</v>
+        <v>4.24781504264749</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6299,22 +6299,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09655958120422171</v>
+        <v>0.09639631099640326</v>
       </c>
       <c r="C60">
-        <v>1074.128431447536</v>
+        <v>1054.355855602782</v>
       </c>
       <c r="D60">
-        <v>1846.784431447536</v>
+        <v>1852.743855602782</v>
       </c>
       <c r="E60">
-        <v>-600.8440000000001</v>
+        <v>-575.1120000000001</v>
       </c>
       <c r="F60">
-        <v>1492.456</v>
+        <v>1518.188</v>
       </c>
       <c r="G60">
         <v>719.8</v>
@@ -6335,28 +6335,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M60">
-        <v>86.26395680000002</v>
+        <v>87.75126640000001</v>
       </c>
       <c r="N60">
-        <v>280.1693765333334</v>
+        <v>278.6820669333334</v>
       </c>
       <c r="O60">
-        <v>67.240650368</v>
+        <v>66.88369606400001</v>
       </c>
       <c r="P60">
-        <v>212.9287261653334</v>
+        <v>211.7983708693334</v>
       </c>
       <c r="Q60">
-        <v>382.3287261653334</v>
+        <v>381.1983708693334</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1692412885814803</v>
+        <v>0.1718994902351299</v>
       </c>
       <c r="T60">
-        <v>2.081397463906363</v>
+        <v>2.126218562616832</v>
       </c>
       <c r="U60">
         <v>0.0578</v>
@@ -6373,7 +6373,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>4.247815042647491</v>
+        <v>4.175818177517873</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6381,22 +6381,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.09639631099640326</v>
+        <v>0.09623304078858479</v>
       </c>
       <c r="C61">
-        <v>1054.355855602782</v>
+        <v>1034.621865431433</v>
       </c>
       <c r="D61">
-        <v>1852.743855602782</v>
+        <v>1858.741865431433</v>
       </c>
       <c r="E61">
-        <v>-575.1120000000001</v>
+        <v>-549.3800000000001</v>
       </c>
       <c r="F61">
-        <v>1518.188</v>
+        <v>1543.92</v>
       </c>
       <c r="G61">
         <v>719.8</v>
@@ -6417,28 +6417,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M61">
-        <v>87.75126640000001</v>
+        <v>89.23857600000001</v>
       </c>
       <c r="N61">
-        <v>278.6820669333334</v>
+        <v>277.1947573333334</v>
       </c>
       <c r="O61">
-        <v>66.88369606400001</v>
+        <v>66.52674176000001</v>
       </c>
       <c r="P61">
-        <v>211.7983708693334</v>
+        <v>210.6680155733334</v>
       </c>
       <c r="Q61">
-        <v>381.1983708693334</v>
+        <v>380.0680155733334</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1718994902351299</v>
+        <v>0.174690601971462</v>
       </c>
       <c r="T61">
-        <v>2.126218562616832</v>
+        <v>2.173280716262824</v>
       </c>
       <c r="U61">
         <v>0.0578</v>
@@ -6455,7 +6455,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>4.175818177517873</v>
+        <v>4.106221207892575</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6463,22 +6463,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.09623304078858479</v>
+        <v>0.09606977058076634</v>
       </c>
       <c r="C62">
-        <v>1034.621865431433</v>
+        <v>1014.926836898455</v>
       </c>
       <c r="D62">
-        <v>1858.741865431433</v>
+        <v>1864.778836898455</v>
       </c>
       <c r="E62">
-        <v>-549.3800000000001</v>
+        <v>-523.6480000000001</v>
       </c>
       <c r="F62">
-        <v>1543.92</v>
+        <v>1569.652</v>
       </c>
       <c r="G62">
         <v>719.8</v>
@@ -6499,28 +6499,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M62">
-        <v>89.23857600000001</v>
+        <v>90.72588560000001</v>
       </c>
       <c r="N62">
-        <v>277.1947573333334</v>
+        <v>275.7074477333334</v>
       </c>
       <c r="O62">
-        <v>66.52674176000001</v>
+        <v>66.16978745600001</v>
       </c>
       <c r="P62">
-        <v>210.6680155733334</v>
+        <v>209.5376602773334</v>
       </c>
       <c r="Q62">
-        <v>380.0680155733334</v>
+        <v>378.9376602773334</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.174690601971462</v>
+        <v>0.1776248476429906</v>
       </c>
       <c r="T62">
-        <v>2.173280716262824</v>
+        <v>2.222756313685534</v>
       </c>
       <c r="U62">
         <v>0.0578</v>
@@ -6537,7 +6537,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>4.106221207892575</v>
+        <v>4.038906106123844</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6545,22 +6545,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.09606977058076634</v>
+        <v>0.09755570037294786</v>
       </c>
       <c r="C63">
-        <v>1014.926836898455</v>
+        <v>935.6561849314273</v>
       </c>
       <c r="D63">
-        <v>1864.778836898455</v>
+        <v>1811.240184931428</v>
       </c>
       <c r="E63">
-        <v>-523.6480000000001</v>
+        <v>-497.9159999999999</v>
       </c>
       <c r="F63">
-        <v>1569.652</v>
+        <v>1595.384</v>
       </c>
       <c r="G63">
         <v>719.8</v>
@@ -6581,45 +6581,45 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M63">
-        <v>90.72588560000001</v>
+        <v>97.79703920000001</v>
       </c>
       <c r="N63">
-        <v>275.7074477333334</v>
+        <v>268.6362941333334</v>
       </c>
       <c r="O63">
-        <v>66.16978745600001</v>
+        <v>64.472710592</v>
       </c>
       <c r="P63">
-        <v>209.5376602773334</v>
+        <v>204.1635835413334</v>
       </c>
       <c r="Q63">
-        <v>378.9376602773334</v>
+        <v>373.5635835413334</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1776248476429906</v>
+        <v>0.1807135272972313</v>
       </c>
       <c r="T63">
-        <v>2.222756313685534</v>
+        <v>2.274835889919966</v>
       </c>
       <c r="U63">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V63">
         <v>0.24</v>
       </c>
       <c r="W63">
-        <v>0.043928</v>
+        <v>0.046588</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y63">
-        <v>4.038906106123844</v>
+        <v>3.74687553253998</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6627,22 +6627,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.09755570037294786</v>
+        <v>0.0974190301651294</v>
       </c>
       <c r="C64">
-        <v>935.6561849314273</v>
+        <v>914.7197529940556</v>
       </c>
       <c r="D64">
-        <v>1811.240184931428</v>
+        <v>1816.035752994056</v>
       </c>
       <c r="E64">
-        <v>-497.9159999999999</v>
+        <v>-472.184</v>
       </c>
       <c r="F64">
-        <v>1595.384</v>
+        <v>1621.116</v>
       </c>
       <c r="G64">
         <v>719.8</v>
@@ -6663,28 +6663,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M64">
-        <v>97.79703920000001</v>
+        <v>99.37441080000001</v>
       </c>
       <c r="N64">
-        <v>268.6362941333334</v>
+        <v>267.0589225333334</v>
       </c>
       <c r="O64">
-        <v>64.472710592</v>
+        <v>64.09414140800001</v>
       </c>
       <c r="P64">
-        <v>204.1635835413334</v>
+        <v>202.9647811253334</v>
       </c>
       <c r="Q64">
-        <v>373.5635835413334</v>
+        <v>372.3647811253334</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1807135272972313</v>
+        <v>0.1839691626084578</v>
       </c>
       <c r="T64">
-        <v>2.274835889919966</v>
+        <v>2.329730578383284</v>
       </c>
       <c r="U64">
         <v>0.0613</v>
@@ -6701,7 +6701,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>3.74687553253998</v>
+        <v>3.687401317737759</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.0974190301651294</v>
+        <v>0.09728235995731094</v>
       </c>
       <c r="C65">
-        <v>914.7197529940556</v>
+        <v>893.8087826433036</v>
       </c>
       <c r="D65">
-        <v>1816.035752994056</v>
+        <v>1820.856782643304</v>
       </c>
       <c r="E65">
-        <v>-472.184</v>
+        <v>-446.452</v>
       </c>
       <c r="F65">
-        <v>1621.116</v>
+        <v>1646.848</v>
       </c>
       <c r="G65">
         <v>719.8</v>
@@ -6745,28 +6745,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M65">
-        <v>99.37441080000001</v>
+        <v>100.9517824</v>
       </c>
       <c r="N65">
-        <v>267.0589225333334</v>
+        <v>265.4815509333334</v>
       </c>
       <c r="O65">
-        <v>64.09414140800001</v>
+        <v>63.71557222400001</v>
       </c>
       <c r="P65">
-        <v>202.9647811253334</v>
+        <v>201.7659787093334</v>
       </c>
       <c r="Q65">
-        <v>372.3647811253334</v>
+        <v>371.1659787093334</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1839691626084578</v>
+        <v>0.187405666548086</v>
       </c>
       <c r="T65">
-        <v>2.329730578383284</v>
+        <v>2.387674971761233</v>
       </c>
       <c r="U65">
         <v>0.0613</v>
@@ -6783,7 +6783,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>3.687401317737759</v>
+        <v>3.629785672148106</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6791,22 +6791,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.09728235995731094</v>
+        <v>0.09714568974949248</v>
       </c>
       <c r="C66">
-        <v>893.8087826433036</v>
+        <v>872.9234771975232</v>
       </c>
       <c r="D66">
-        <v>1820.856782643304</v>
+        <v>1825.703477197523</v>
       </c>
       <c r="E66">
-        <v>-446.452</v>
+        <v>-420.72</v>
       </c>
       <c r="F66">
-        <v>1646.848</v>
+        <v>1672.58</v>
       </c>
       <c r="G66">
         <v>719.8</v>
@@ -6827,28 +6827,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M66">
-        <v>100.9517824</v>
+        <v>102.529154</v>
       </c>
       <c r="N66">
-        <v>265.4815509333334</v>
+        <v>263.9041793333334</v>
       </c>
       <c r="O66">
-        <v>63.71557222400001</v>
+        <v>63.33700304000001</v>
       </c>
       <c r="P66">
-        <v>201.7659787093334</v>
+        <v>200.5671762933334</v>
       </c>
       <c r="Q66">
-        <v>371.1659787093334</v>
+        <v>369.9671762933334</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.187405666548086</v>
+        <v>0.1910385421414071</v>
       </c>
       <c r="T66">
-        <v>2.387674971761233</v>
+        <v>2.448930473332208</v>
       </c>
       <c r="U66">
         <v>0.0613</v>
@@ -6865,7 +6865,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>3.629785672148106</v>
+        <v>3.57394281565352</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6873,22 +6873,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.09714568974949248</v>
+        <v>0.09700901954167401</v>
       </c>
       <c r="C67">
-        <v>872.9234771975232</v>
+        <v>852.0640421455869</v>
       </c>
       <c r="D67">
-        <v>1825.703477197523</v>
+        <v>1830.576042145587</v>
       </c>
       <c r="E67">
-        <v>-420.72</v>
+        <v>-394.9879999999998</v>
       </c>
       <c r="F67">
-        <v>1672.58</v>
+        <v>1698.312</v>
       </c>
       <c r="G67">
         <v>719.8</v>
@@ -6909,28 +6909,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M67">
-        <v>102.529154</v>
+        <v>104.1065256</v>
       </c>
       <c r="N67">
-        <v>263.9041793333334</v>
+        <v>262.3268077333333</v>
       </c>
       <c r="O67">
-        <v>63.33700304000001</v>
+        <v>62.958433856</v>
       </c>
       <c r="P67">
-        <v>200.5671762933334</v>
+        <v>199.3683738773333</v>
       </c>
       <c r="Q67">
-        <v>369.9671762933334</v>
+        <v>368.7683738773334</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1910385421414071</v>
+        <v>0.1948851162990412</v>
       </c>
       <c r="T67">
-        <v>2.448930473332208</v>
+        <v>2.513789239701474</v>
       </c>
       <c r="U67">
         <v>0.0613</v>
@@ -6947,7 +6947,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>3.57394281565352</v>
+        <v>3.519792166931496</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6955,22 +6955,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.09700901954167401</v>
+        <v>0.09829810933385558</v>
       </c>
       <c r="C68">
-        <v>852.0640421455869</v>
+        <v>781.3822921510623</v>
       </c>
       <c r="D68">
-        <v>1830.576042145587</v>
+        <v>1785.626292151063</v>
       </c>
       <c r="E68">
-        <v>-394.9879999999998</v>
+        <v>-369.2559999999999</v>
       </c>
       <c r="F68">
-        <v>1698.312</v>
+        <v>1724.044</v>
       </c>
       <c r="G68">
         <v>719.8</v>
@@ -6991,45 +6991,45 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M68">
-        <v>104.1065256</v>
+        <v>110.5112204</v>
       </c>
       <c r="N68">
-        <v>262.3268077333333</v>
+        <v>255.9221129333334</v>
       </c>
       <c r="O68">
-        <v>62.958433856</v>
+        <v>61.42130710400001</v>
       </c>
       <c r="P68">
-        <v>199.3683738773333</v>
+        <v>194.5008058293334</v>
       </c>
       <c r="Q68">
-        <v>368.7683738773334</v>
+        <v>363.9008058293334</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1948851162990412</v>
+        <v>0.1989648161631987</v>
       </c>
       <c r="T68">
-        <v>2.513789239701474</v>
+        <v>2.582578840396152</v>
       </c>
       <c r="U68">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V68">
         <v>0.24</v>
       </c>
       <c r="W68">
-        <v>0.046588</v>
+        <v>0.048716</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y68">
-        <v>3.519792166931496</v>
+        <v>3.315802069753754</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7037,22 +7037,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09829810933385558</v>
+        <v>0.0981827191260371</v>
       </c>
       <c r="C69">
-        <v>781.3822921510623</v>
+        <v>759.5837227246398</v>
       </c>
       <c r="D69">
-        <v>1785.626292151063</v>
+        <v>1789.55972272464</v>
       </c>
       <c r="E69">
-        <v>-369.2559999999999</v>
+        <v>-343.5239999999999</v>
       </c>
       <c r="F69">
-        <v>1724.044</v>
+        <v>1749.776</v>
       </c>
       <c r="G69">
         <v>719.8</v>
@@ -7073,28 +7073,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M69">
-        <v>110.5112204</v>
+        <v>112.1606416</v>
       </c>
       <c r="N69">
-        <v>255.9221129333334</v>
+        <v>254.2726917333334</v>
       </c>
       <c r="O69">
-        <v>61.42130710400001</v>
+        <v>61.02544601600001</v>
       </c>
       <c r="P69">
-        <v>194.5008058293334</v>
+        <v>193.2472457173334</v>
       </c>
       <c r="Q69">
-        <v>363.9008058293334</v>
+        <v>362.6472457173334</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1989648161631987</v>
+        <v>0.203299497268866</v>
       </c>
       <c r="T69">
-        <v>2.582578840396152</v>
+        <v>2.655667791134245</v>
       </c>
       <c r="U69">
         <v>0.0641</v>
@@ -7111,7 +7111,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>3.315802069753754</v>
+        <v>3.267040274610317</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7119,22 +7119,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.0981827191260371</v>
+        <v>0.09806732891821865</v>
       </c>
       <c r="C70">
-        <v>759.5837227246398</v>
+        <v>737.8025209112434</v>
       </c>
       <c r="D70">
-        <v>1789.55972272464</v>
+        <v>1793.510520911244</v>
       </c>
       <c r="E70">
-        <v>-343.5239999999999</v>
+        <v>-317.7919999999999</v>
       </c>
       <c r="F70">
-        <v>1749.776</v>
+        <v>1775.508</v>
       </c>
       <c r="G70">
         <v>719.8</v>
@@ -7155,28 +7155,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M70">
-        <v>112.1606416</v>
+        <v>113.8100628</v>
       </c>
       <c r="N70">
-        <v>254.2726917333334</v>
+        <v>252.6232705333334</v>
       </c>
       <c r="O70">
-        <v>61.02544601600001</v>
+        <v>60.62958492800001</v>
       </c>
       <c r="P70">
-        <v>193.2472457173334</v>
+        <v>191.9936856053334</v>
       </c>
       <c r="Q70">
-        <v>362.6472457173334</v>
+        <v>361.3936856053334</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.203299497268866</v>
+        <v>0.2079138352200602</v>
       </c>
       <c r="T70">
-        <v>2.655667791134245</v>
+        <v>2.733472158048991</v>
       </c>
       <c r="U70">
         <v>0.0641</v>
@@ -7193,7 +7193,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>3.267040274610317</v>
+        <v>3.219691864833356</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7201,22 +7201,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.09806732891821865</v>
+        <v>0.09795193871040017</v>
       </c>
       <c r="C71">
-        <v>737.8025209112434</v>
+        <v>716.0388019924469</v>
       </c>
       <c r="D71">
-        <v>1793.510520911244</v>
+        <v>1797.478801992447</v>
       </c>
       <c r="E71">
-        <v>-317.7919999999999</v>
+        <v>-292.0599999999997</v>
       </c>
       <c r="F71">
-        <v>1775.508</v>
+        <v>1801.24</v>
       </c>
       <c r="G71">
         <v>719.8</v>
@@ -7237,28 +7237,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M71">
-        <v>113.8100628</v>
+        <v>115.459484</v>
       </c>
       <c r="N71">
-        <v>252.6232705333334</v>
+        <v>250.9738493333334</v>
       </c>
       <c r="O71">
-        <v>60.62958492800001</v>
+        <v>60.23372384</v>
       </c>
       <c r="P71">
-        <v>191.9936856053334</v>
+        <v>190.7401254933334</v>
       </c>
       <c r="Q71">
-        <v>361.3936856053334</v>
+        <v>360.1401254933334</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2079138352200602</v>
+        <v>0.2128357957013339</v>
       </c>
       <c r="T71">
-        <v>2.733472158048991</v>
+        <v>2.816463482758053</v>
       </c>
       <c r="U71">
         <v>0.0641</v>
@@ -7275,7 +7275,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>3.219691864833356</v>
+        <v>3.173696266764308</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7283,22 +7283,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.09795193871040017</v>
+        <v>0.09783654850258172</v>
       </c>
       <c r="C72">
-        <v>716.0388019924469</v>
+        <v>694.2926822723596</v>
       </c>
       <c r="D72">
-        <v>1797.478801992447</v>
+        <v>1801.46468227236</v>
       </c>
       <c r="E72">
-        <v>-292.0599999999997</v>
+        <v>-266.3279999999997</v>
       </c>
       <c r="F72">
-        <v>1801.24</v>
+        <v>1826.972</v>
       </c>
       <c r="G72">
         <v>719.8</v>
@@ -7319,28 +7319,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M72">
-        <v>115.459484</v>
+        <v>117.1089052</v>
       </c>
       <c r="N72">
-        <v>250.9738493333334</v>
+        <v>249.3244281333334</v>
       </c>
       <c r="O72">
-        <v>60.23372384</v>
+        <v>59.83786275200001</v>
       </c>
       <c r="P72">
-        <v>190.7401254933334</v>
+        <v>189.4865653813333</v>
       </c>
       <c r="Q72">
-        <v>360.1401254933334</v>
+        <v>358.8865653813334</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2128357957013339</v>
+        <v>0.2180972017330405</v>
       </c>
       <c r="T72">
-        <v>2.816463482758053</v>
+        <v>2.905178347102223</v>
       </c>
       <c r="U72">
         <v>0.0641</v>
@@ -7357,7 +7357,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>3.173696266764308</v>
+        <v>3.128996319345092</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7365,22 +7365,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.09783654850258172</v>
+        <v>0.09772115829476324</v>
       </c>
       <c r="C73">
-        <v>694.2926822723598</v>
+        <v>672.5642790889974</v>
       </c>
       <c r="D73">
-        <v>1801.46468227236</v>
+        <v>1805.468279088998</v>
       </c>
       <c r="E73">
-        <v>-266.328</v>
+        <v>-240.596</v>
       </c>
       <c r="F73">
-        <v>1826.972</v>
+        <v>1852.704</v>
       </c>
       <c r="G73">
         <v>719.8</v>
@@ -7401,28 +7401,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M73">
-        <v>117.1089052</v>
+        <v>118.7583264</v>
       </c>
       <c r="N73">
-        <v>249.3244281333334</v>
+        <v>247.6750069333334</v>
       </c>
       <c r="O73">
-        <v>59.83786275200001</v>
+        <v>59.44200166400001</v>
       </c>
       <c r="P73">
-        <v>189.4865653813333</v>
+        <v>188.2330052693334</v>
       </c>
       <c r="Q73">
-        <v>358.8865653813334</v>
+        <v>357.6330052693334</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2180972017330404</v>
+        <v>0.2237344224812973</v>
       </c>
       <c r="T73">
-        <v>2.905178347102222</v>
+        <v>3.000229987470974</v>
       </c>
       <c r="U73">
         <v>0.0641</v>
@@ -7439,7 +7439,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>3.128996319345092</v>
+        <v>3.085538037131966</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7447,22 +7447,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.09772115829476324</v>
+        <v>0.09760576808694479</v>
       </c>
       <c r="C74">
-        <v>672.5642790889974</v>
+        <v>650.8537108257892</v>
       </c>
       <c r="D74">
-        <v>1805.468279088998</v>
+        <v>1809.489710825789</v>
       </c>
       <c r="E74">
-        <v>-240.596</v>
+        <v>-214.864</v>
       </c>
       <c r="F74">
-        <v>1852.704</v>
+        <v>1878.436</v>
       </c>
       <c r="G74">
         <v>719.8</v>
@@ -7483,28 +7483,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M74">
-        <v>118.7583264</v>
+        <v>120.4077476</v>
       </c>
       <c r="N74">
-        <v>247.6750069333334</v>
+        <v>246.0255857333334</v>
       </c>
       <c r="O74">
-        <v>59.44200166400001</v>
+        <v>59.04614057600001</v>
       </c>
       <c r="P74">
-        <v>188.2330052693334</v>
+        <v>186.9794451573334</v>
       </c>
       <c r="Q74">
-        <v>357.6330052693334</v>
+        <v>356.3794451573334</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2237344224812973</v>
+        <v>0.2297892151368325</v>
       </c>
       <c r="T74">
-        <v>3.000229987470974</v>
+        <v>3.102322490089265</v>
       </c>
       <c r="U74">
         <v>0.0641</v>
@@ -7521,7 +7521,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>3.085538037131966</v>
+        <v>3.043270392787692</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7529,22 +7529,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.09760576808694479</v>
+        <v>0.09749037787912632</v>
       </c>
       <c r="C75">
-        <v>650.8537108257892</v>
+        <v>629.1610969232529</v>
       </c>
       <c r="D75">
-        <v>1809.489710825789</v>
+        <v>1813.529096923253</v>
       </c>
       <c r="E75">
-        <v>-214.864</v>
+        <v>-189.1320000000001</v>
       </c>
       <c r="F75">
-        <v>1878.436</v>
+        <v>1904.168</v>
       </c>
       <c r="G75">
         <v>719.8</v>
@@ -7565,28 +7565,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M75">
-        <v>120.4077476</v>
+        <v>122.0571688</v>
       </c>
       <c r="N75">
-        <v>246.0255857333334</v>
+        <v>244.3761645333334</v>
       </c>
       <c r="O75">
-        <v>59.04614057600001</v>
+        <v>58.65027948800001</v>
       </c>
       <c r="P75">
-        <v>186.9794451573334</v>
+        <v>185.7258850453334</v>
       </c>
       <c r="Q75">
-        <v>356.3794451573334</v>
+        <v>355.1258850453333</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2297892151368325</v>
+        <v>0.2363097610735627</v>
       </c>
       <c r="T75">
-        <v>3.102322490089265</v>
+        <v>3.212268262139731</v>
       </c>
       <c r="U75">
         <v>0.0641</v>
@@ -7603,7 +7603,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>3.043270392787692</v>
+        <v>3.002145117209481</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7611,22 +7611,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.09749037787912632</v>
+        <v>0.1018209876713079</v>
       </c>
       <c r="C76">
-        <v>629.1610969232529</v>
+        <v>463.2372296962417</v>
       </c>
       <c r="D76">
-        <v>1813.529096923253</v>
+        <v>1673.337229696242</v>
       </c>
       <c r="E76">
-        <v>-189.1320000000001</v>
+        <v>-163.4000000000001</v>
       </c>
       <c r="F76">
-        <v>1904.168</v>
+        <v>1929.9</v>
       </c>
       <c r="G76">
         <v>719.8</v>
@@ -7647,45 +7647,45 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M76">
-        <v>122.0571688</v>
+        <v>138.75981</v>
       </c>
       <c r="N76">
-        <v>244.3761645333334</v>
+        <v>227.6735233333334</v>
       </c>
       <c r="O76">
-        <v>58.65027948800001</v>
+        <v>54.64164560000001</v>
       </c>
       <c r="P76">
-        <v>185.7258850453334</v>
+        <v>173.0318777333334</v>
       </c>
       <c r="Q76">
-        <v>355.1258850453333</v>
+        <v>342.4318777333334</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2363097610735627</v>
+        <v>0.2433519506852315</v>
       </c>
       <c r="T76">
-        <v>3.212268262139731</v>
+        <v>3.331009695954235</v>
       </c>
       <c r="U76">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V76">
         <v>0.24</v>
       </c>
       <c r="W76">
-        <v>0.048716</v>
+        <v>0.05464400000000001</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y76">
-        <v>3.002145117209481</v>
+        <v>2.640774251084182</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7693,22 +7693,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1018209876713079</v>
+        <v>0.1017648774634894</v>
       </c>
       <c r="C77">
-        <v>463.2372296962417</v>
+        <v>439.1829122708152</v>
       </c>
       <c r="D77">
-        <v>1673.337229696242</v>
+        <v>1675.014912270816</v>
       </c>
       <c r="E77">
-        <v>-163.4000000000001</v>
+        <v>-137.6679999999999</v>
       </c>
       <c r="F77">
-        <v>1929.9</v>
+        <v>1955.632</v>
       </c>
       <c r="G77">
         <v>719.8</v>
@@ -7729,28 +7729,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M77">
-        <v>138.75981</v>
+        <v>140.6099408</v>
       </c>
       <c r="N77">
-        <v>227.6735233333334</v>
+        <v>225.8233925333334</v>
       </c>
       <c r="O77">
-        <v>54.64164560000001</v>
+        <v>54.197614208</v>
       </c>
       <c r="P77">
-        <v>173.0318777333334</v>
+        <v>171.6257783253334</v>
       </c>
       <c r="Q77">
-        <v>342.4318777333334</v>
+        <v>341.0257783253334</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2433519506852315</v>
+        <v>0.2509809894312058</v>
       </c>
       <c r="T77">
-        <v>3.331009695954235</v>
+        <v>3.45964624925328</v>
       </c>
       <c r="U77">
         <v>0.07190000000000001</v>
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.640774251084182</v>
+        <v>2.606027221464653</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7775,22 +7775,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1017648774634894</v>
+        <v>0.1017087672556709</v>
       </c>
       <c r="C78">
-        <v>439.1829122708152</v>
+        <v>415.1319622999947</v>
       </c>
       <c r="D78">
-        <v>1675.014912270816</v>
+        <v>1676.695962299995</v>
       </c>
       <c r="E78">
-        <v>-137.6679999999999</v>
+        <v>-111.9359999999999</v>
       </c>
       <c r="F78">
-        <v>1955.632</v>
+        <v>1981.364</v>
       </c>
       <c r="G78">
         <v>719.8</v>
@@ -7811,28 +7811,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M78">
-        <v>140.6099408</v>
+        <v>142.4600716</v>
       </c>
       <c r="N78">
-        <v>225.8233925333334</v>
+        <v>223.9732617333334</v>
       </c>
       <c r="O78">
-        <v>54.197614208</v>
+        <v>53.75358281600001</v>
       </c>
       <c r="P78">
-        <v>171.6257783253334</v>
+        <v>170.2196789173334</v>
       </c>
       <c r="Q78">
-        <v>341.0257783253334</v>
+        <v>339.6196789173334</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2509809894312058</v>
+        <v>0.2592734228507432</v>
       </c>
       <c r="T78">
-        <v>3.45964624925328</v>
+        <v>3.599468589795721</v>
       </c>
       <c r="U78">
         <v>0.07190000000000001</v>
@@ -7849,7 +7849,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.606027221464653</v>
+        <v>2.572182712094982</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7857,22 +7857,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1017087672556709</v>
+        <v>0.1016526570478525</v>
       </c>
       <c r="C79">
-        <v>415.1319622999947</v>
+        <v>391.084389932729</v>
       </c>
       <c r="D79">
-        <v>1676.695962299995</v>
+        <v>1678.380389932729</v>
       </c>
       <c r="E79">
-        <v>-111.9359999999999</v>
+        <v>-86.20399999999995</v>
       </c>
       <c r="F79">
-        <v>1981.364</v>
+        <v>2007.096</v>
       </c>
       <c r="G79">
         <v>719.8</v>
@@ -7893,28 +7893,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M79">
-        <v>142.4600716</v>
+        <v>144.3102024</v>
       </c>
       <c r="N79">
-        <v>223.9732617333334</v>
+        <v>222.1231309333334</v>
       </c>
       <c r="O79">
-        <v>53.75358281600001</v>
+        <v>53.30955142400001</v>
       </c>
       <c r="P79">
-        <v>170.2196789173334</v>
+        <v>168.8135795093334</v>
       </c>
       <c r="Q79">
-        <v>339.6196789173334</v>
+        <v>338.2135795093334</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2592734228507432</v>
+        <v>0.2683197138538749</v>
       </c>
       <c r="T79">
-        <v>3.599468589795721</v>
+        <v>3.752002052205657</v>
       </c>
       <c r="U79">
         <v>0.07190000000000001</v>
@@ -7931,7 +7931,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.572182712094982</v>
+        <v>2.539206010657867</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7939,22 +7939,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1016526570478525</v>
+        <v>0.101596546840034</v>
       </c>
       <c r="C80">
-        <v>391.084389932729</v>
+        <v>367.0402053587907</v>
       </c>
       <c r="D80">
-        <v>1678.380389932729</v>
+        <v>1680.068205358791</v>
       </c>
       <c r="E80">
-        <v>-86.20399999999995</v>
+        <v>-60.47199999999998</v>
       </c>
       <c r="F80">
-        <v>2007.096</v>
+        <v>2032.828</v>
       </c>
       <c r="G80">
         <v>719.8</v>
@@ -7975,28 +7975,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M80">
-        <v>144.3102024</v>
+        <v>146.1603332</v>
       </c>
       <c r="N80">
-        <v>222.1231309333334</v>
+        <v>220.2730001333334</v>
       </c>
       <c r="O80">
-        <v>53.30955142400001</v>
+        <v>52.86552003200001</v>
       </c>
       <c r="P80">
-        <v>168.8135795093334</v>
+        <v>167.4074801013334</v>
       </c>
       <c r="Q80">
-        <v>338.2135795093334</v>
+        <v>336.8074801013333</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2683197138538749</v>
+        <v>0.2782275563811143</v>
       </c>
       <c r="T80">
-        <v>3.752002052205657</v>
+        <v>3.919062511035587</v>
       </c>
       <c r="U80">
         <v>0.07190000000000001</v>
@@ -8013,7 +8013,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.539206010657867</v>
+        <v>2.507064162421691</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8021,22 +8021,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.101596546840034</v>
+        <v>0.1039116366322156</v>
       </c>
       <c r="C81">
-        <v>367.0402053587907</v>
+        <v>274.3765376618135</v>
       </c>
       <c r="D81">
-        <v>1680.068205358791</v>
+        <v>1613.136537661814</v>
       </c>
       <c r="E81">
-        <v>-60.47199999999998</v>
+        <v>-34.73999999999978</v>
       </c>
       <c r="F81">
-        <v>2032.828</v>
+        <v>2058.56</v>
       </c>
       <c r="G81">
         <v>719.8</v>
@@ -8057,45 +8057,45 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M81">
-        <v>146.1603332</v>
+        <v>156.038848</v>
       </c>
       <c r="N81">
-        <v>220.2730001333334</v>
+        <v>210.3944853333334</v>
       </c>
       <c r="O81">
-        <v>52.86552003200001</v>
+        <v>50.49467648</v>
       </c>
       <c r="P81">
-        <v>167.4074801013334</v>
+        <v>159.8998088533334</v>
       </c>
       <c r="Q81">
-        <v>336.8074801013333</v>
+        <v>329.2998088533334</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2782275563811143</v>
+        <v>0.2891261831610778</v>
       </c>
       <c r="T81">
-        <v>3.919062511035587</v>
+        <v>4.10282901574851</v>
       </c>
       <c r="U81">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V81">
         <v>0.24</v>
       </c>
       <c r="W81">
-        <v>0.05464400000000001</v>
+        <v>0.05760800000000001</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y81">
-        <v>2.507064162421691</v>
+        <v>2.348346825358089</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8103,22 +8103,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1039116366322156</v>
+        <v>0.1038851664243971</v>
       </c>
       <c r="C82">
-        <v>274.3765376618135</v>
+        <v>249.3796661295446</v>
       </c>
       <c r="D82">
-        <v>1613.136537661814</v>
+        <v>1613.871666129545</v>
       </c>
       <c r="E82">
-        <v>-34.73999999999978</v>
+        <v>-9.007999999999811</v>
       </c>
       <c r="F82">
-        <v>2058.56</v>
+        <v>2084.292</v>
       </c>
       <c r="G82">
         <v>719.8</v>
@@ -8139,28 +8139,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M82">
-        <v>156.038848</v>
+        <v>157.9893336</v>
       </c>
       <c r="N82">
-        <v>210.3944853333334</v>
+        <v>208.4439997333334</v>
       </c>
       <c r="O82">
-        <v>50.49467648</v>
+        <v>50.02655993600001</v>
       </c>
       <c r="P82">
-        <v>159.8998088533334</v>
+        <v>158.4174397973333</v>
       </c>
       <c r="Q82">
-        <v>329.2998088533334</v>
+        <v>327.8174397973333</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2891261831610778</v>
+        <v>0.3011720338126163</v>
       </c>
       <c r="T82">
-        <v>4.10282901574851</v>
+        <v>4.305939363062793</v>
       </c>
       <c r="U82">
         <v>0.07580000000000001</v>
@@ -8177,7 +8177,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.348346825358089</v>
+        <v>2.319354889242557</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8185,22 +8185,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1038851664243971</v>
+        <v>0.1038586962165786</v>
       </c>
       <c r="C83">
-        <v>249.3796661295446</v>
+        <v>224.3834649190217</v>
       </c>
       <c r="D83">
-        <v>1613.871666129545</v>
+        <v>1614.607464919022</v>
       </c>
       <c r="E83">
-        <v>-9.007999999999811</v>
+        <v>16.72400000000016</v>
       </c>
       <c r="F83">
-        <v>2084.292</v>
+        <v>2110.024</v>
       </c>
       <c r="G83">
         <v>719.8</v>
@@ -8221,28 +8221,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M83">
-        <v>157.9893336</v>
+        <v>159.9398192</v>
       </c>
       <c r="N83">
-        <v>208.4439997333334</v>
+        <v>206.4935141333333</v>
       </c>
       <c r="O83">
-        <v>50.02655993600001</v>
+        <v>49.558443392</v>
       </c>
       <c r="P83">
-        <v>158.4174397973333</v>
+        <v>156.9350707413333</v>
       </c>
       <c r="Q83">
-        <v>327.8174397973333</v>
+        <v>326.3350707413333</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3011720338126163</v>
+        <v>0.3145563123143258</v>
       </c>
       <c r="T83">
-        <v>4.305939363062793</v>
+        <v>4.531617526745329</v>
       </c>
       <c r="U83">
         <v>0.07580000000000001</v>
@@ -8259,7 +8259,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.319354889242557</v>
+        <v>2.291070073520086</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8267,22 +8267,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1038586962165786</v>
+        <v>0.1038322260087602</v>
       </c>
       <c r="C84">
-        <v>224.3834649190217</v>
+        <v>199.3879349475055</v>
       </c>
       <c r="D84">
-        <v>1614.607464919022</v>
+        <v>1615.343934947506</v>
       </c>
       <c r="E84">
-        <v>16.72400000000016</v>
+        <v>42.45600000000013</v>
       </c>
       <c r="F84">
-        <v>2110.024</v>
+        <v>2135.756</v>
       </c>
       <c r="G84">
         <v>719.8</v>
@@ -8303,28 +8303,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M84">
-        <v>159.9398192</v>
+        <v>161.8903048</v>
       </c>
       <c r="N84">
-        <v>206.4935141333333</v>
+        <v>204.5430285333334</v>
       </c>
       <c r="O84">
-        <v>49.558443392</v>
+        <v>49.090326848</v>
       </c>
       <c r="P84">
-        <v>156.9350707413333</v>
+        <v>155.4527016853334</v>
       </c>
       <c r="Q84">
-        <v>326.3350707413333</v>
+        <v>324.8527016853334</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3145563123143258</v>
+        <v>0.3295152118162364</v>
       </c>
       <c r="T84">
-        <v>4.531617526745329</v>
+        <v>4.783846062625812</v>
       </c>
       <c r="U84">
         <v>0.07580000000000001</v>
@@ -8341,7 +8341,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.291070073520086</v>
+        <v>2.263466819622254</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8349,22 +8349,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1038322260087602</v>
+        <v>0.1038057558009417</v>
       </c>
       <c r="C85">
-        <v>199.3879349475055</v>
+        <v>174.3930771339305</v>
       </c>
       <c r="D85">
-        <v>1615.343934947506</v>
+        <v>1616.081077133931</v>
       </c>
       <c r="E85">
-        <v>42.45600000000013</v>
+        <v>68.1880000000001</v>
       </c>
       <c r="F85">
-        <v>2135.756</v>
+        <v>2161.488</v>
       </c>
       <c r="G85">
         <v>719.8</v>
@@ -8385,28 +8385,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M85">
-        <v>161.8903048</v>
+        <v>163.8407904</v>
       </c>
       <c r="N85">
-        <v>204.5430285333334</v>
+        <v>202.5925429333334</v>
       </c>
       <c r="O85">
-        <v>49.090326848</v>
+        <v>48.62221030400001</v>
       </c>
       <c r="P85">
-        <v>155.4527016853334</v>
+        <v>153.9703326293334</v>
       </c>
       <c r="Q85">
-        <v>324.8527016853334</v>
+        <v>323.3703326293333</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3295152118162364</v>
+        <v>0.3463439737558858</v>
       </c>
       <c r="T85">
-        <v>4.783846062625812</v>
+        <v>5.067603165491354</v>
       </c>
       <c r="U85">
         <v>0.07580000000000001</v>
@@ -8423,7 +8423,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.263466819622254</v>
+        <v>2.236520786055323</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8431,22 +8431,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1038057558009417</v>
+        <v>0.1037792855931233</v>
       </c>
       <c r="C86">
-        <v>174.3930771339305</v>
+        <v>149.39889239891</v>
       </c>
       <c r="D86">
-        <v>1616.081077133931</v>
+        <v>1616.81889239891</v>
       </c>
       <c r="E86">
-        <v>68.1880000000001</v>
+        <v>93.92000000000007</v>
       </c>
       <c r="F86">
-        <v>2161.488</v>
+        <v>2187.22</v>
       </c>
       <c r="G86">
         <v>719.8</v>
@@ -8467,28 +8467,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M86">
-        <v>163.8407904</v>
+        <v>165.791276</v>
       </c>
       <c r="N86">
-        <v>202.5925429333334</v>
+        <v>200.6420573333334</v>
       </c>
       <c r="O86">
-        <v>48.62221030400001</v>
+        <v>48.15409376</v>
       </c>
       <c r="P86">
-        <v>153.9703326293334</v>
+        <v>152.4879635733334</v>
       </c>
       <c r="Q86">
-        <v>323.3703326293333</v>
+        <v>321.8879635733334</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3463439737558856</v>
+        <v>0.3654165706208216</v>
       </c>
       <c r="T86">
-        <v>5.06760316549135</v>
+        <v>5.389194548738965</v>
       </c>
       <c r="U86">
         <v>0.07580000000000001</v>
@@ -8505,7 +8505,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.236520786055323</v>
+        <v>2.210208776807613</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8513,22 +8513,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1037792855931233</v>
+        <v>0.1037528153853048</v>
       </c>
       <c r="C87">
-        <v>149.39889239891</v>
+        <v>124.4053816647393</v>
       </c>
       <c r="D87">
-        <v>1616.81889239891</v>
+        <v>1617.55738166474</v>
       </c>
       <c r="E87">
-        <v>93.92000000000007</v>
+        <v>119.652</v>
       </c>
       <c r="F87">
-        <v>2187.22</v>
+        <v>2212.952</v>
       </c>
       <c r="G87">
         <v>719.8</v>
@@ -8549,28 +8549,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M87">
-        <v>165.791276</v>
+        <v>167.7417616</v>
       </c>
       <c r="N87">
-        <v>200.6420573333334</v>
+        <v>198.6915717333334</v>
       </c>
       <c r="O87">
-        <v>48.15409376</v>
+        <v>47.68597721600001</v>
       </c>
       <c r="P87">
-        <v>152.4879635733334</v>
+        <v>151.0055945173333</v>
       </c>
       <c r="Q87">
-        <v>321.8879635733334</v>
+        <v>320.4055945173334</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3654165706208216</v>
+        <v>0.3872138241807484</v>
       </c>
       <c r="T87">
-        <v>5.389194548738965</v>
+        <v>5.75672755816481</v>
       </c>
       <c r="U87">
         <v>0.07580000000000001</v>
@@ -8587,7 +8587,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.210208776807613</v>
+        <v>2.184508674751711</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8595,22 +8595,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1037528153853048</v>
+        <v>0.1037263451774863</v>
       </c>
       <c r="C88">
-        <v>124.4053816647393</v>
+        <v>99.41254585539809</v>
       </c>
       <c r="D88">
-        <v>1617.55738166474</v>
+        <v>1618.296545855398</v>
       </c>
       <c r="E88">
-        <v>119.652</v>
+        <v>145.384</v>
       </c>
       <c r="F88">
-        <v>2212.952</v>
+        <v>2238.684</v>
       </c>
       <c r="G88">
         <v>719.8</v>
@@ -8631,28 +8631,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M88">
-        <v>167.7417616</v>
+        <v>169.6922472</v>
       </c>
       <c r="N88">
-        <v>198.6915717333334</v>
+        <v>196.7410861333334</v>
       </c>
       <c r="O88">
-        <v>47.68597721600001</v>
+        <v>47.21786067200001</v>
       </c>
       <c r="P88">
-        <v>151.0055945173333</v>
+        <v>149.5232254613334</v>
       </c>
       <c r="Q88">
-        <v>320.4055945173334</v>
+        <v>318.9232254613333</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3872138241807484</v>
+        <v>0.4123645013652794</v>
       </c>
       <c r="T88">
-        <v>5.75672755816481</v>
+        <v>6.180804107502323</v>
       </c>
       <c r="U88">
         <v>0.07580000000000001</v>
@@ -8669,7 +8669,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.184508674751711</v>
+        <v>2.159399379639622</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8677,22 +8677,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1037263451774863</v>
+        <v>0.1036998749696679</v>
       </c>
       <c r="C89">
-        <v>99.41254585539809</v>
+        <v>74.42038589655795</v>
       </c>
       <c r="D89">
-        <v>1618.296545855398</v>
+        <v>1619.036385896558</v>
       </c>
       <c r="E89">
-        <v>145.384</v>
+        <v>171.116</v>
       </c>
       <c r="F89">
-        <v>2238.684</v>
+        <v>2264.416</v>
       </c>
       <c r="G89">
         <v>719.8</v>
@@ -8713,28 +8713,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M89">
-        <v>169.6922472</v>
+        <v>171.6427328</v>
       </c>
       <c r="N89">
-        <v>196.7410861333334</v>
+        <v>194.7906005333334</v>
       </c>
       <c r="O89">
-        <v>47.21786067200001</v>
+        <v>46.749744128</v>
       </c>
       <c r="P89">
-        <v>149.5232254613334</v>
+        <v>148.0408564053334</v>
       </c>
       <c r="Q89">
-        <v>318.9232254613333</v>
+        <v>317.4408564053334</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4123645013652794</v>
+        <v>0.4417069580805655</v>
       </c>
       <c r="T89">
-        <v>6.180804107502323</v>
+        <v>6.675560081729422</v>
       </c>
       <c r="U89">
         <v>0.07580000000000001</v>
@@ -8751,7 +8751,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.159399379639622</v>
+        <v>2.134860750325535</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8759,22 +8759,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1036998749696679</v>
+        <v>0.1036734047618494</v>
       </c>
       <c r="C90">
-        <v>74.42038589655795</v>
+        <v>49.42890271558235</v>
       </c>
       <c r="D90">
-        <v>1619.036385896558</v>
+        <v>1619.776902715583</v>
       </c>
       <c r="E90">
-        <v>171.116</v>
+        <v>196.848</v>
       </c>
       <c r="F90">
-        <v>2264.416</v>
+        <v>2290.148</v>
       </c>
       <c r="G90">
         <v>719.8</v>
@@ -8795,28 +8795,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M90">
-        <v>171.6427328</v>
+        <v>173.5932184</v>
       </c>
       <c r="N90">
-        <v>194.7906005333334</v>
+        <v>192.8401149333334</v>
       </c>
       <c r="O90">
-        <v>46.749744128</v>
+        <v>46.28162758400001</v>
       </c>
       <c r="P90">
-        <v>148.0408564053334</v>
+        <v>146.5584873493334</v>
       </c>
       <c r="Q90">
-        <v>317.4408564053334</v>
+        <v>315.9584873493334</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4417069580805655</v>
+        <v>0.4763844069259036</v>
       </c>
       <c r="T90">
-        <v>6.675560081729422</v>
+        <v>7.260271687634175</v>
       </c>
       <c r="U90">
         <v>0.07580000000000001</v>
@@ -8833,7 +8833,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.134860750325535</v>
+        <v>2.110873550883675</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8841,22 +8841,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1036734047618494</v>
+        <v>0.1036469345540309</v>
       </c>
       <c r="C91">
-        <v>49.42890271558235</v>
+        <v>24.43809724153198</v>
       </c>
       <c r="D91">
-        <v>1619.776902715583</v>
+        <v>1620.518097241532</v>
       </c>
       <c r="E91">
-        <v>196.848</v>
+        <v>222.5799999999999</v>
       </c>
       <c r="F91">
-        <v>2290.148</v>
+        <v>2315.88</v>
       </c>
       <c r="G91">
         <v>719.8</v>
@@ -8877,28 +8877,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M91">
-        <v>173.5932184</v>
+        <v>175.543704</v>
       </c>
       <c r="N91">
-        <v>192.8401149333334</v>
+        <v>190.8896293333334</v>
       </c>
       <c r="O91">
-        <v>46.28162758400001</v>
+        <v>45.81351104000001</v>
       </c>
       <c r="P91">
-        <v>146.5584873493334</v>
+        <v>145.0761182933334</v>
       </c>
       <c r="Q91">
-        <v>315.9584873493334</v>
+        <v>314.4761182933333</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4763844069259036</v>
+        <v>0.5179973455403094</v>
       </c>
       <c r="T91">
-        <v>7.260271687634175</v>
+        <v>7.96192561471988</v>
       </c>
       <c r="U91">
         <v>0.07580000000000001</v>
@@ -8915,7 +8915,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.110873550883675</v>
+        <v>2.087419400318301</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8923,22 +8923,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1036469345540309</v>
+        <v>0.1036204643462125</v>
       </c>
       <c r="C92">
-        <v>24.43809724153198</v>
+        <v>-0.5520295948299463</v>
       </c>
       <c r="D92">
-        <v>1620.518097241532</v>
+        <v>1621.259970405171</v>
       </c>
       <c r="E92">
-        <v>222.5799999999999</v>
+        <v>248.3120000000004</v>
       </c>
       <c r="F92">
-        <v>2315.88</v>
+        <v>2341.612000000001</v>
       </c>
       <c r="G92">
         <v>719.8</v>
@@ -8959,28 +8959,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M92">
-        <v>175.543704</v>
+        <v>177.4941896000001</v>
       </c>
       <c r="N92">
-        <v>190.8896293333334</v>
+        <v>188.9391437333333</v>
       </c>
       <c r="O92">
-        <v>45.81351104000001</v>
+        <v>45.345394496</v>
       </c>
       <c r="P92">
-        <v>145.0761182933334</v>
+        <v>143.5937492373333</v>
       </c>
       <c r="Q92">
-        <v>314.4761182933333</v>
+        <v>312.9937492373333</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5179973455403094</v>
+        <v>0.5688576038468053</v>
       </c>
       <c r="T92">
-        <v>7.96192561471988</v>
+        <v>8.819502636713519</v>
       </c>
       <c r="U92">
         <v>0.07580000000000001</v>
@@ -8997,7 +8997,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.087419400318301</v>
+        <v>2.064480725589528</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9005,22 +9005,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1036204643462125</v>
+        <v>0.103593994138394</v>
       </c>
       <c r="C93">
-        <v>-0.5520295948299463</v>
+        <v>-25.54147686103579</v>
       </c>
       <c r="D93">
-        <v>1621.259970405171</v>
+        <v>1622.002523138965</v>
       </c>
       <c r="E93">
-        <v>248.3120000000004</v>
+        <v>274.0440000000003</v>
       </c>
       <c r="F93">
-        <v>2341.612000000001</v>
+        <v>2367.344000000001</v>
       </c>
       <c r="G93">
         <v>719.8</v>
@@ -9041,28 +9041,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M93">
-        <v>177.4941896000001</v>
+        <v>179.4446752000001</v>
       </c>
       <c r="N93">
-        <v>188.9391437333333</v>
+        <v>186.9886581333333</v>
       </c>
       <c r="O93">
-        <v>45.345394496</v>
+        <v>44.877277952</v>
       </c>
       <c r="P93">
-        <v>143.5937492373333</v>
+        <v>142.1113801813333</v>
       </c>
       <c r="Q93">
-        <v>312.9937492373333</v>
+        <v>311.5113801813334</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5688576038468053</v>
+        <v>0.6324329267299253</v>
       </c>
       <c r="T93">
-        <v>8.819502636713519</v>
+        <v>9.891473914205569</v>
       </c>
       <c r="U93">
         <v>0.07580000000000001</v>
@@ -9079,7 +9079,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.064480725589528</v>
+        <v>2.042040717702685</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9087,22 +9087,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.103593994138394</v>
+        <v>0.1035675239305756</v>
       </c>
       <c r="C94">
-        <v>-25.54147686103579</v>
+        <v>-50.53024362290762</v>
       </c>
       <c r="D94">
-        <v>1622.002523138965</v>
+        <v>1622.745756377093</v>
       </c>
       <c r="E94">
-        <v>274.0440000000003</v>
+        <v>299.7760000000003</v>
       </c>
       <c r="F94">
-        <v>2367.344000000001</v>
+        <v>2393.076</v>
       </c>
       <c r="G94">
         <v>719.8</v>
@@ -9123,28 +9123,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M94">
-        <v>179.4446752000001</v>
+        <v>181.3951608</v>
       </c>
       <c r="N94">
-        <v>186.9886581333333</v>
+        <v>185.0381725333334</v>
       </c>
       <c r="O94">
-        <v>44.877277952</v>
+        <v>44.409161408</v>
       </c>
       <c r="P94">
-        <v>142.1113801813333</v>
+        <v>140.6290111253334</v>
       </c>
       <c r="Q94">
-        <v>311.5113801813334</v>
+        <v>310.0290111253333</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6324329267299253</v>
+        <v>0.7141726275796511</v>
       </c>
       <c r="T94">
-        <v>9.891473914205569</v>
+        <v>11.26972269955249</v>
       </c>
       <c r="U94">
         <v>0.07580000000000001</v>
@@ -9161,7 +9161,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>2.042040717702685</v>
+        <v>2.020083290630613</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9169,22 +9169,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1035675239305756</v>
+        <v>0.1136855337227571</v>
       </c>
       <c r="C95">
-        <v>-50.53024362290762</v>
+        <v>-318.1246339268432</v>
       </c>
       <c r="D95">
-        <v>1622.745756377093</v>
+        <v>1380.883366073157</v>
       </c>
       <c r="E95">
-        <v>299.7760000000003</v>
+        <v>325.5080000000003</v>
       </c>
       <c r="F95">
-        <v>2393.076</v>
+        <v>2418.808</v>
       </c>
       <c r="G95">
         <v>719.8</v>
@@ -9205,45 +9205,45 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M95">
-        <v>181.3951608</v>
+        <v>217.69272</v>
       </c>
       <c r="N95">
-        <v>185.0381725333334</v>
+        <v>148.7406133333334</v>
       </c>
       <c r="O95">
-        <v>44.409161408</v>
+        <v>35.6977472</v>
       </c>
       <c r="P95">
-        <v>140.6290111253334</v>
+        <v>113.0428661333333</v>
       </c>
       <c r="Q95">
-        <v>310.0290111253333</v>
+        <v>282.4428661333334</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7141726275796511</v>
+        <v>0.8231588953792853</v>
       </c>
       <c r="T95">
-        <v>11.26972269955249</v>
+        <v>13.10738774668172</v>
       </c>
       <c r="U95">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V95">
         <v>0.24</v>
       </c>
       <c r="W95">
-        <v>0.05760800000000001</v>
+        <v>0.0684</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y95">
-        <v>2.020083290630613</v>
+        <v>1.683259473873694</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9251,22 +9251,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1136855337227571</v>
+        <v>0.1137669835149386</v>
       </c>
       <c r="C96">
-        <v>-318.1246339268432</v>
+        <v>-345.5114471519864</v>
       </c>
       <c r="D96">
-        <v>1380.883366073157</v>
+        <v>1379.228552848014</v>
       </c>
       <c r="E96">
-        <v>325.5080000000003</v>
+        <v>351.2400000000002</v>
       </c>
       <c r="F96">
-        <v>2418.808</v>
+        <v>2444.54</v>
       </c>
       <c r="G96">
         <v>719.8</v>
@@ -9287,28 +9287,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M96">
-        <v>217.69272</v>
+        <v>220.0086</v>
       </c>
       <c r="N96">
-        <v>148.7406133333334</v>
+        <v>146.4247333333334</v>
       </c>
       <c r="O96">
-        <v>35.6977472</v>
+        <v>35.14193600000001</v>
       </c>
       <c r="P96">
-        <v>113.0428661333333</v>
+        <v>111.2827973333333</v>
       </c>
       <c r="Q96">
-        <v>282.4428661333334</v>
+        <v>280.6827973333334</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8231588953792853</v>
+        <v>0.9757396702987737</v>
       </c>
       <c r="T96">
-        <v>13.10738774668172</v>
+        <v>15.68011881266264</v>
       </c>
       <c r="U96">
         <v>0.09</v>
@@ -9325,7 +9325,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>1.683259473873694</v>
+        <v>1.665540953096076</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9333,22 +9333,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1137669835149386</v>
+        <v>0.1138484333071202</v>
       </c>
       <c r="C97">
-        <v>-345.5114471519864</v>
+        <v>-372.8942989576894</v>
       </c>
       <c r="D97">
-        <v>1379.228552848014</v>
+        <v>1377.577701042311</v>
       </c>
       <c r="E97">
-        <v>351.2400000000002</v>
+        <v>376.9720000000002</v>
       </c>
       <c r="F97">
-        <v>2444.54</v>
+        <v>2470.272</v>
       </c>
       <c r="G97">
         <v>719.8</v>
@@ -9369,28 +9369,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M97">
-        <v>220.0086</v>
+        <v>222.32448</v>
       </c>
       <c r="N97">
-        <v>146.4247333333334</v>
+        <v>144.1088533333334</v>
       </c>
       <c r="O97">
-        <v>35.14193600000001</v>
+        <v>34.58612480000001</v>
       </c>
       <c r="P97">
-        <v>111.2827973333333</v>
+        <v>109.5227285333334</v>
       </c>
       <c r="Q97">
-        <v>280.6827973333334</v>
+        <v>278.9227285333334</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.9757396702987737</v>
+        <v>1.204610832678006</v>
       </c>
       <c r="T97">
-        <v>15.68011881266264</v>
+        <v>19.53921541163402</v>
       </c>
       <c r="U97">
         <v>0.09</v>
@@ -9407,7 +9407,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>1.665540953096076</v>
+        <v>1.648191568167992</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9415,22 +9415,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1138484333071202</v>
+        <v>0.1139298830993017</v>
       </c>
       <c r="C98">
-        <v>-372.8942989576894</v>
+        <v>-400.2732035516733</v>
       </c>
       <c r="D98">
-        <v>1377.577701042311</v>
+        <v>1375.930796448327</v>
       </c>
       <c r="E98">
-        <v>376.9720000000002</v>
+        <v>402.7040000000002</v>
       </c>
       <c r="F98">
-        <v>2470.272</v>
+        <v>2496.004</v>
       </c>
       <c r="G98">
         <v>719.8</v>
@@ -9451,28 +9451,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M98">
-        <v>222.32448</v>
+        <v>224.64036</v>
       </c>
       <c r="N98">
-        <v>144.1088533333334</v>
+        <v>141.7929733333334</v>
       </c>
       <c r="O98">
-        <v>34.58612480000001</v>
+        <v>34.03031360000001</v>
       </c>
       <c r="P98">
-        <v>109.5227285333334</v>
+        <v>107.7626597333334</v>
       </c>
       <c r="Q98">
-        <v>278.9227285333334</v>
+        <v>277.1626597333334</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.204610832678003</v>
+        <v>1.586062769976722</v>
       </c>
       <c r="T98">
-        <v>19.53921541163397</v>
+        <v>25.97104307658625</v>
       </c>
       <c r="U98">
         <v>0.09</v>
@@ -9489,7 +9489,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>1.648191568167992</v>
+        <v>1.631199902516776</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9497,22 +9497,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1139298830993017</v>
+        <v>0.1140113328914832</v>
       </c>
       <c r="C99">
-        <v>-400.2732035516733</v>
+        <v>-427.6481750737971</v>
       </c>
       <c r="D99">
-        <v>1375.930796448327</v>
+        <v>1374.287824926203</v>
       </c>
       <c r="E99">
-        <v>402.7040000000002</v>
+        <v>428.4360000000001</v>
       </c>
       <c r="F99">
-        <v>2496.004</v>
+        <v>2521.736</v>
       </c>
       <c r="G99">
         <v>719.8</v>
@@ -9533,28 +9533,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M99">
-        <v>224.64036</v>
+        <v>226.95624</v>
       </c>
       <c r="N99">
-        <v>141.7929733333334</v>
+        <v>139.4770933333334</v>
       </c>
       <c r="O99">
-        <v>34.03031360000001</v>
+        <v>33.47450240000001</v>
       </c>
       <c r="P99">
-        <v>107.7626597333334</v>
+        <v>106.0025909333334</v>
       </c>
       <c r="Q99">
-        <v>277.1626597333334</v>
+        <v>275.4025909333334</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.586062769976722</v>
+        <v>2.348966644574159</v>
       </c>
       <c r="T99">
-        <v>25.97104307658625</v>
+        <v>38.8346984064908</v>
       </c>
       <c r="U99">
         <v>0.09</v>
@@ -9571,7 +9571,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>1.631199902516776</v>
+        <v>1.614555005552319</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9579,22 +9579,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1140113328914832</v>
+        <v>0.1140927826836648</v>
       </c>
       <c r="C100">
-        <v>-427.6481750737971</v>
+        <v>-455.0192275964682</v>
       </c>
       <c r="D100">
-        <v>1374.287824926203</v>
+        <v>1372.648772403532</v>
       </c>
       <c r="E100">
-        <v>428.4360000000001</v>
+        <v>454.1680000000001</v>
       </c>
       <c r="F100">
-        <v>2521.736</v>
+        <v>2547.468</v>
       </c>
       <c r="G100">
         <v>719.8</v>
@@ -9615,28 +9615,28 @@
         <v>366.4333333333334</v>
       </c>
       <c r="M100">
-        <v>226.95624</v>
+        <v>229.27212</v>
       </c>
       <c r="N100">
-        <v>139.4770933333334</v>
+        <v>137.1612133333334</v>
       </c>
       <c r="O100">
-        <v>33.47450240000001</v>
+        <v>32.9186912</v>
       </c>
       <c r="P100">
-        <v>106.0025909333334</v>
+        <v>104.2425221333334</v>
       </c>
       <c r="Q100">
-        <v>275.4025909333334</v>
+        <v>273.6425221333334</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.348966644574159</v>
+        <v>4.637678268366473</v>
       </c>
       <c r="T100">
-        <v>38.8346984064908</v>
+        <v>77.42566439620447</v>
       </c>
       <c r="U100">
         <v>0.09</v>
@@ -9653,91 +9653,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>1.614555005552319</v>
+        <v>1.598246369132598</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1140927826836648</v>
-      </c>
-      <c r="C101">
-        <v>-455.0192275964682</v>
-      </c>
-      <c r="D101">
-        <v>1372.648772403532</v>
-      </c>
-      <c r="E101">
-        <v>454.1680000000001</v>
-      </c>
-      <c r="F101">
-        <v>2547.468</v>
-      </c>
-      <c r="G101">
-        <v>719.8</v>
-      </c>
-      <c r="H101">
-        <v>479.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>535.8333333333334</v>
-      </c>
-      <c r="K101">
-        <v>169.4</v>
-      </c>
-      <c r="L101">
-        <v>366.4333333333334</v>
-      </c>
-      <c r="M101">
-        <v>229.27212</v>
-      </c>
-      <c r="N101">
-        <v>137.1612133333334</v>
-      </c>
-      <c r="O101">
-        <v>32.9186912</v>
-      </c>
-      <c r="P101">
-        <v>104.2425221333334</v>
-      </c>
-      <c r="Q101">
-        <v>273.6425221333334</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.637678268366473</v>
-      </c>
-      <c r="T101">
-        <v>77.42566439620447</v>
-      </c>
-      <c r="U101">
-        <v>0.09</v>
-      </c>
-      <c r="V101">
-        <v>0.24</v>
-      </c>
-      <c r="W101">
-        <v>0.0684</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B3/B-</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>1.598246369132598</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
